--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 25,06,26 днрсч пок зпф от Рекуты.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 25,06,26 днрсч пок зпф от Рекуты.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4EAFAB-D38E-4FD0-8A88-E908DF43279F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF97F4F9-ECFF-4E8D-B0FE-8DAB494D50FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$69</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -558,7 +550,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,6 +589,22 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -678,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -701,8 +709,13 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1023,17 +1036,21 @@
     <col min="15" max="16" width="6.7109375" customWidth="1"/>
     <col min="17" max="17" width="7" customWidth="1"/>
     <col min="18" max="18" width="7" style="22" customWidth="1"/>
-    <col min="19" max="21" width="7" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="7" style="28" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
     <col min="22" max="22" width="15" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
     <col min="25" max="29" width="6" customWidth="1"/>
-    <col min="30" max="30" width="29.85546875" customWidth="1"/>
+    <col min="30" max="30" width="16.85546875" customWidth="1"/>
     <col min="31" max="31" width="7" customWidth="1"/>
     <col min="32" max="32" width="6" style="19" customWidth="1"/>
     <col min="33" max="34" width="7" customWidth="1"/>
     <col min="35" max="36" width="5" customWidth="1"/>
     <col min="37" max="37" width="6" style="19" customWidth="1"/>
-    <col min="38" max="53" width="3" customWidth="1"/>
+    <col min="38" max="38" width="3" customWidth="1"/>
+    <col min="39" max="39" width="7.7109375" customWidth="1"/>
+    <col min="40" max="53" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -1058,7 +1075,7 @@
       <c r="S1" s="23">
         <v>0.84</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="24"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -1115,7 +1132,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="24"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -1303,7 +1320,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="T4" s="24"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -1402,7 +1419,7 @@
         <f t="shared" si="0"/>
         <v>29242.12</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="25">
         <f t="shared" si="0"/>
         <v>29251.399999999998</v>
       </c>
@@ -1454,7 +1471,10 @@
         <v>35.852380952380955</v>
       </c>
       <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
+      <c r="AM5" s="4">
+        <f>SUM(AM6:AM500)</f>
+        <v>2075.36</v>
+      </c>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
@@ -1518,7 +1538,7 @@
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
       <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
+      <c r="T6" s="26"/>
       <c r="U6" s="13"/>
       <c r="V6" s="11"/>
       <c r="W6" s="11">
@@ -1617,7 +1637,7 @@
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
       <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
+      <c r="T7" s="26"/>
       <c r="U7" s="13"/>
       <c r="V7" s="11"/>
       <c r="W7" s="11">
@@ -1714,7 +1734,7 @@
       <c r="Q8" s="13"/>
       <c r="R8" s="13"/>
       <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
+      <c r="T8" s="26"/>
       <c r="U8" s="13"/>
       <c r="V8" s="11"/>
       <c r="W8" s="11" t="e">
@@ -1813,7 +1833,7 @@
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
       <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
+      <c r="T9" s="26"/>
       <c r="U9" s="13"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11">
@@ -1917,7 +1937,7 @@
         <f>R10*$S$1</f>
         <v>606.3119999999999</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="27">
         <f t="shared" ref="T10:T18" si="5">AF10*AG10</f>
         <v>672</v>
       </c>
@@ -1973,7 +1993,10 @@
         <v>0.8</v>
       </c>
       <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
+      <c r="AM10" s="1">
+        <f>P10*G10</f>
+        <v>22.979999999999997</v>
+      </c>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
@@ -2042,7 +2065,7 @@
         <f>R11*$S$1</f>
         <v>840</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11" s="27">
         <f t="shared" si="5"/>
         <v>840</v>
       </c>
@@ -2102,7 +2125,10 @@
         <v>1</v>
       </c>
       <c r="AL11" s="1"/>
-      <c r="AM11" s="1"/>
+      <c r="AM11" s="1">
+        <f t="shared" ref="AM11:AM68" si="10">P11*G11</f>
+        <v>19.656000000000002</v>
+      </c>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
@@ -2164,7 +2190,7 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="5">
+      <c r="T12" s="27">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2220,7 +2246,10 @@
         <v>0</v>
       </c>
       <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
+      <c r="AM12" s="1">
+        <f t="shared" si="10"/>
+        <v>22.271999999999998</v>
+      </c>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
@@ -2286,10 +2315,10 @@
         <v>427</v>
       </c>
       <c r="S13" s="5">
-        <f t="shared" ref="S13" si="10">14*P13-O13-F13</f>
+        <f t="shared" ref="S13" si="11">14*P13-O13-F13</f>
         <v>427</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="27">
         <f t="shared" si="5"/>
         <v>504</v>
       </c>
@@ -2345,7 +2374,10 @@
         <v>0.6</v>
       </c>
       <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
+      <c r="AM13" s="1">
+        <f t="shared" si="10"/>
+        <v>43.199999999999996</v>
+      </c>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
@@ -2411,10 +2443,10 @@
         <v>1273.6000000000001</v>
       </c>
       <c r="S14" s="5">
-        <f t="shared" ref="S14:S15" si="11">R14*$S$1</f>
+        <f t="shared" ref="S14:S15" si="12">R14*$S$1</f>
         <v>1069.8240000000001</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T14" s="27">
         <f t="shared" si="5"/>
         <v>1008</v>
       </c>
@@ -2470,7 +2502,10 @@
         <v>1.2</v>
       </c>
       <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
+      <c r="AM14" s="1">
+        <f t="shared" si="10"/>
+        <v>34.896000000000001</v>
+      </c>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
@@ -2538,10 +2573,10 @@
         <v>771</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>647.64</v>
       </c>
-      <c r="T15" s="5">
+      <c r="T15" s="27">
         <f t="shared" si="5"/>
         <v>672</v>
       </c>
@@ -2597,7 +2632,10 @@
         <v>0.8</v>
       </c>
       <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
+      <c r="AM15" s="1">
+        <f t="shared" si="10"/>
+        <v>36.479999999999997</v>
+      </c>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
@@ -2659,7 +2697,7 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
-      <c r="T16" s="5">
+      <c r="T16" s="27">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2715,7 +2753,10 @@
         <v>0</v>
       </c>
       <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
+      <c r="AM16" s="1">
+        <f t="shared" si="10"/>
+        <v>26.783999999999999</v>
+      </c>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
@@ -2784,7 +2825,7 @@
         <f>R17*$S$1</f>
         <v>2100</v>
       </c>
-      <c r="T17" s="5">
+      <c r="T17" s="27">
         <f t="shared" si="5"/>
         <v>2016</v>
       </c>
@@ -2844,7 +2885,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
+      <c r="AM17" s="1">
+        <f t="shared" si="10"/>
+        <v>18.431999999999999</v>
+      </c>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
@@ -2906,7 +2950,7 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="5">
+      <c r="T18" s="27">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2962,7 +3006,10 @@
         <v>0</v>
       </c>
       <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
+      <c r="AM18" s="1">
+        <f t="shared" si="10"/>
+        <v>5.903999999999999</v>
+      </c>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
@@ -3022,7 +3069,7 @@
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
+      <c r="T19" s="26"/>
       <c r="U19" s="13"/>
       <c r="V19" s="11"/>
       <c r="W19" s="11">
@@ -3057,7 +3104,10 @@
       <c r="AJ19" s="11"/>
       <c r="AK19" s="11"/>
       <c r="AL19" s="1"/>
-      <c r="AM19" s="1"/>
+      <c r="AM19" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
@@ -3121,8 +3171,8 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
-      <c r="T20" s="5">
-        <f t="shared" ref="T20:T31" si="12">AF20*AG20</f>
+      <c r="T20" s="27">
+        <f t="shared" ref="T20:T31" si="13">AF20*AG20</f>
         <v>0</v>
       </c>
       <c r="U20" s="5"/>
@@ -3152,18 +3202,18 @@
       </c>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1">
-        <f t="shared" ref="AE20:AE31" si="13">G20*S20</f>
+        <f t="shared" ref="AE20:AE31" si="14">G20*S20</f>
         <v>0</v>
       </c>
       <c r="AF20" s="17">
         <v>6</v>
       </c>
       <c r="AG20" s="1">
-        <f t="shared" ref="AG20:AG31" si="14">MROUND(S20, AF20*AI20)/AF20</f>
+        <f t="shared" ref="AG20:AG31" si="15">MROUND(S20, AF20*AI20)/AF20</f>
         <v>0</v>
       </c>
       <c r="AH20" s="1">
-        <f t="shared" ref="AH20:AH31" si="15">AG20*AF20*G20</f>
+        <f t="shared" ref="AH20:AH31" si="16">AG20*AF20*G20</f>
         <v>0</v>
       </c>
       <c r="AI20" s="1">
@@ -3173,11 +3223,14 @@
         <v>84</v>
       </c>
       <c r="AK20" s="17">
-        <f t="shared" ref="AK20:AK31" si="16">AG20/AJ20</f>
+        <f t="shared" ref="AK20:AK31" si="17">AG20/AJ20</f>
         <v>0</v>
       </c>
       <c r="AL20" s="1"/>
-      <c r="AM20" s="1"/>
+      <c r="AM20" s="1">
+        <f t="shared" si="10"/>
+        <v>9.48</v>
+      </c>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
@@ -3239,8 +3292,8 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
-      <c r="T21" s="5">
-        <f t="shared" si="12"/>
+      <c r="T21" s="27">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U21" s="5"/>
@@ -3270,20 +3323,20 @@
       </c>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF21" s="17">
         <v>12</v>
       </c>
       <c r="AG21" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH21" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="AH21" s="1">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="AI21" s="1">
         <v>14</v>
       </c>
@@ -3291,11 +3344,14 @@
         <v>70</v>
       </c>
       <c r="AK21" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
+      <c r="AM21" s="1">
+        <f t="shared" si="10"/>
+        <v>33.28</v>
+      </c>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
@@ -3364,8 +3420,8 @@
         <f>R22*$S$1</f>
         <v>437.30400000000009</v>
       </c>
-      <c r="T22" s="5">
-        <f t="shared" si="12"/>
+      <c r="T22" s="27">
+        <f t="shared" si="13"/>
         <v>504</v>
       </c>
       <c r="U22" s="5"/>
@@ -3395,18 +3451,18 @@
       </c>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>87.46080000000002</v>
       </c>
       <c r="AF22" s="17">
         <v>12</v>
       </c>
       <c r="AG22" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42</v>
       </c>
       <c r="AH22" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>100.80000000000001</v>
       </c>
       <c r="AI22" s="1">
@@ -3416,11 +3472,14 @@
         <v>70</v>
       </c>
       <c r="AK22" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.6</v>
       </c>
       <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
+      <c r="AM22" s="1">
+        <f t="shared" si="10"/>
+        <v>17.28</v>
+      </c>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
@@ -3486,11 +3545,11 @@
         <v>189.89999999999998</v>
       </c>
       <c r="S23" s="5">
-        <f t="shared" ref="S23:S31" si="17">14*P23-O23-F23</f>
+        <f t="shared" ref="S23:S31" si="18">14*P23-O23-F23</f>
         <v>189.89999999999998</v>
       </c>
-      <c r="T23" s="5">
-        <f t="shared" si="12"/>
+      <c r="T23" s="27">
+        <f t="shared" si="13"/>
         <v>180</v>
       </c>
       <c r="U23" s="5"/>
@@ -3520,18 +3579,18 @@
       </c>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>189.89999999999998</v>
       </c>
       <c r="AF23" s="17">
         <v>5</v>
       </c>
       <c r="AG23" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>36</v>
       </c>
       <c r="AH23" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>180</v>
       </c>
       <c r="AI23" s="1">
@@ -3541,11 +3600,14 @@
         <v>84</v>
       </c>
       <c r="AK23" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
+      <c r="AM23" s="1">
+        <f t="shared" si="10"/>
+        <v>42.1</v>
+      </c>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
@@ -3611,11 +3673,11 @@
         <v>163.89999999999998</v>
       </c>
       <c r="S24" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>163.89999999999998</v>
       </c>
-      <c r="T24" s="5">
-        <f t="shared" si="12"/>
+      <c r="T24" s="27">
+        <f t="shared" si="13"/>
         <v>132</v>
       </c>
       <c r="U24" s="5"/>
@@ -3645,18 +3707,18 @@
       </c>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>163.89999999999998</v>
       </c>
       <c r="AF24" s="17">
         <v>5.5</v>
       </c>
       <c r="AG24" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="AH24" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>132</v>
       </c>
       <c r="AI24" s="1">
@@ -3666,11 +3728,14 @@
         <v>84</v>
       </c>
       <c r="AK24" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL24" s="1"/>
-      <c r="AM24" s="1"/>
+      <c r="AM24" s="1">
+        <f t="shared" si="10"/>
+        <v>39.6</v>
+      </c>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
@@ -3736,11 +3801,11 @@
         <v>370.80000000000007</v>
       </c>
       <c r="S25" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>370.80000000000007</v>
       </c>
-      <c r="T25" s="5">
-        <f t="shared" si="12"/>
+      <c r="T25" s="27">
+        <f t="shared" si="13"/>
         <v>378</v>
       </c>
       <c r="U25" s="5"/>
@@ -3770,18 +3835,18 @@
       </c>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>370.80000000000007</v>
       </c>
       <c r="AF25" s="17">
         <v>3</v>
       </c>
       <c r="AG25" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>126</v>
       </c>
       <c r="AH25" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>378</v>
       </c>
       <c r="AI25" s="1">
@@ -3791,11 +3856,14 @@
         <v>126</v>
       </c>
       <c r="AK25" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AL25" s="1"/>
-      <c r="AM25" s="1"/>
+      <c r="AM25" s="1">
+        <f t="shared" si="10"/>
+        <v>40.200000000000003</v>
+      </c>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
@@ -3864,8 +3932,8 @@
         <f>R26*$S$1</f>
         <v>537.76800000000003</v>
       </c>
-      <c r="T26" s="5">
-        <f t="shared" si="12"/>
+      <c r="T26" s="27">
+        <f t="shared" si="13"/>
         <v>504</v>
       </c>
       <c r="U26" s="5"/>
@@ -3895,18 +3963,18 @@
       </c>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>134.44200000000001</v>
       </c>
       <c r="AF26" s="17">
         <v>6</v>
       </c>
       <c r="AG26" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>84</v>
       </c>
       <c r="AH26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>126</v>
       </c>
       <c r="AI26" s="1">
@@ -3916,11 +3984,14 @@
         <v>140</v>
       </c>
       <c r="AK26" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.6</v>
       </c>
       <c r="AL26" s="1"/>
-      <c r="AM26" s="1"/>
+      <c r="AM26" s="1">
+        <f t="shared" si="10"/>
+        <v>21.45</v>
+      </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
@@ -3982,8 +4053,8 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="5">
-        <f t="shared" si="12"/>
+      <c r="T27" s="27">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U27" s="5"/>
@@ -4013,20 +4084,20 @@
       </c>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF27" s="17">
         <v>6</v>
       </c>
       <c r="AG27" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AH27" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="AH27" s="1">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="AI27" s="1">
         <v>14</v>
       </c>
@@ -4034,11 +4105,14 @@
         <v>140</v>
       </c>
       <c r="AK27" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AL27" s="1"/>
-      <c r="AM27" s="1"/>
+      <c r="AM27" s="1">
+        <f t="shared" si="10"/>
+        <v>19.2</v>
+      </c>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
@@ -4104,11 +4178,11 @@
         <v>342</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>342</v>
       </c>
-      <c r="T28" s="5">
-        <f t="shared" si="12"/>
+      <c r="T28" s="27">
+        <f t="shared" si="13"/>
         <v>360</v>
       </c>
       <c r="U28" s="5"/>
@@ -4138,18 +4212,18 @@
       </c>
       <c r="AD28" s="1"/>
       <c r="AE28" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>342</v>
       </c>
       <c r="AF28" s="17">
         <v>6</v>
       </c>
       <c r="AG28" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>60</v>
       </c>
       <c r="AH28" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>360</v>
       </c>
       <c r="AI28" s="1">
@@ -4159,11 +4233,14 @@
         <v>84</v>
       </c>
       <c r="AK28" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="AL28" s="1"/>
-      <c r="AM28" s="1"/>
+      <c r="AM28" s="1">
+        <f t="shared" si="10"/>
+        <v>66</v>
+      </c>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
@@ -4232,8 +4309,8 @@
         <f>U29</f>
         <v>2500</v>
       </c>
-      <c r="T29" s="5">
-        <f t="shared" si="12"/>
+      <c r="T29" s="27">
+        <f t="shared" si="13"/>
         <v>2520</v>
       </c>
       <c r="U29" s="21">
@@ -4269,18 +4346,18 @@
         <v>167</v>
       </c>
       <c r="AE29" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>575</v>
       </c>
       <c r="AF29" s="17">
         <v>12</v>
       </c>
       <c r="AG29" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>210</v>
       </c>
       <c r="AH29" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>579.6</v>
       </c>
       <c r="AI29" s="1">
@@ -4290,11 +4367,14 @@
         <v>70</v>
       </c>
       <c r="AK29" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="AL29" s="1"/>
-      <c r="AM29" s="1"/>
+      <c r="AM29" s="1">
+        <f t="shared" si="10"/>
+        <v>32.246000000000002</v>
+      </c>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
@@ -4363,8 +4443,8 @@
         <f>R30*$S$1</f>
         <v>871.92</v>
       </c>
-      <c r="T30" s="5">
-        <f t="shared" si="12"/>
+      <c r="T30" s="27">
+        <f t="shared" si="13"/>
         <v>840</v>
       </c>
       <c r="U30" s="5"/>
@@ -4394,18 +4474,18 @@
       </c>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>217.98</v>
       </c>
       <c r="AF30" s="17">
         <v>12</v>
       </c>
       <c r="AG30" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>70</v>
       </c>
       <c r="AH30" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>210</v>
       </c>
       <c r="AI30" s="1">
@@ -4415,11 +4495,14 @@
         <v>70</v>
       </c>
       <c r="AK30" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AL30" s="1"/>
-      <c r="AM30" s="1"/>
+      <c r="AM30" s="1">
+        <f t="shared" si="10"/>
+        <v>46</v>
+      </c>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
@@ -4486,11 +4569,11 @@
         <v>314.60000000000014</v>
       </c>
       <c r="S31" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>314.60000000000014</v>
       </c>
-      <c r="T31" s="5">
-        <f t="shared" si="12"/>
+      <c r="T31" s="27">
+        <f t="shared" si="13"/>
         <v>336</v>
       </c>
       <c r="U31" s="5"/>
@@ -4520,18 +4603,18 @@
       </c>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>78.650000000000034</v>
       </c>
       <c r="AF31" s="17">
         <v>12</v>
       </c>
       <c r="AG31" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
       <c r="AH31" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AI31" s="1">
@@ -4541,11 +4624,14 @@
         <v>70</v>
       </c>
       <c r="AK31" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
       <c r="AL31" s="1"/>
-      <c r="AM31" s="1"/>
+      <c r="AM31" s="1">
+        <f t="shared" si="10"/>
+        <v>32.1</v>
+      </c>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
@@ -4601,7 +4687,7 @@
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
+      <c r="T32" s="26"/>
       <c r="U32" s="13"/>
       <c r="V32" s="11"/>
       <c r="W32" s="11" t="e">
@@ -4636,7 +4722,10 @@
       <c r="AJ32" s="11"/>
       <c r="AK32" s="11"/>
       <c r="AL32" s="1"/>
-      <c r="AM32" s="1"/>
+      <c r="AM32" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
@@ -4702,11 +4791,11 @@
         <v>462.60000000000014</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" ref="S33:S38" si="18">14*P33-O33-F33</f>
+        <f t="shared" ref="S33:S38" si="19">14*P33-O33-F33</f>
         <v>462.60000000000014</v>
       </c>
-      <c r="T33" s="5">
-        <f t="shared" ref="T33:T49" si="19">AF33*AG33</f>
+      <c r="T33" s="27">
+        <f t="shared" ref="T33:T49" si="20">AF33*AG33</f>
         <v>504</v>
       </c>
       <c r="U33" s="5"/>
@@ -4736,18 +4825,18 @@
       </c>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1">
-        <f t="shared" ref="AE33:AE49" si="20">G33*S33</f>
+        <f t="shared" ref="AE33:AE49" si="21">G33*S33</f>
         <v>115.65000000000003</v>
       </c>
       <c r="AF33" s="17">
         <v>12</v>
       </c>
       <c r="AG33" s="1">
-        <f t="shared" ref="AG33:AG49" si="21">MROUND(S33, AF33*AI33)/AF33</f>
+        <f t="shared" ref="AG33:AG49" si="22">MROUND(S33, AF33*AI33)/AF33</f>
         <v>42</v>
       </c>
       <c r="AH33" s="1">
-        <f t="shared" ref="AH33:AH49" si="22">AG33*AF33*G33</f>
+        <f t="shared" ref="AH33:AH49" si="23">AG33*AF33*G33</f>
         <v>126</v>
       </c>
       <c r="AI33" s="1">
@@ -4757,11 +4846,14 @@
         <v>70</v>
       </c>
       <c r="AK33" s="17">
-        <f t="shared" ref="AK33:AK49" si="23">AG33/AJ33</f>
+        <f t="shared" ref="AK33:AK49" si="24">AG33/AJ33</f>
         <v>0.6</v>
       </c>
       <c r="AL33" s="1"/>
-      <c r="AM33" s="1"/>
+      <c r="AM33" s="1">
+        <f t="shared" si="10"/>
+        <v>28.6</v>
+      </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
@@ -4830,8 +4922,8 @@
         <f>16*P34-O34-F34</f>
         <v>115.60000000000002</v>
       </c>
-      <c r="T34" s="5">
-        <f t="shared" si="19"/>
+      <c r="T34" s="27">
+        <f t="shared" si="20"/>
         <v>168</v>
       </c>
       <c r="U34" s="5"/>
@@ -4861,18 +4953,18 @@
       </c>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>28.900000000000006</v>
       </c>
       <c r="AF34" s="17">
         <v>12</v>
       </c>
       <c r="AG34" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AH34" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>42</v>
       </c>
       <c r="AI34" s="1">
@@ -4882,11 +4974,14 @@
         <v>70</v>
       </c>
       <c r="AK34" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.2</v>
       </c>
       <c r="AL34" s="1"/>
-      <c r="AM34" s="1"/>
+      <c r="AM34" s="1">
+        <f t="shared" si="10"/>
+        <v>10.15</v>
+      </c>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
@@ -4952,11 +5047,11 @@
         <v>425.4</v>
       </c>
       <c r="S35" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>425.4</v>
       </c>
-      <c r="T35" s="5">
-        <f t="shared" si="19"/>
+      <c r="T35" s="27">
+        <f t="shared" si="20"/>
         <v>384</v>
       </c>
       <c r="U35" s="5"/>
@@ -4986,18 +5081,18 @@
       </c>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>297.77999999999997</v>
       </c>
       <c r="AF35" s="17">
         <v>8</v>
       </c>
       <c r="AG35" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>48</v>
       </c>
       <c r="AH35" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>268.79999999999995</v>
       </c>
       <c r="AI35" s="1">
@@ -5007,11 +5102,14 @@
         <v>84</v>
       </c>
       <c r="AK35" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="AL35" s="1"/>
-      <c r="AM35" s="1"/>
+      <c r="AM35" s="1">
+        <f t="shared" si="10"/>
+        <v>34.72</v>
+      </c>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
@@ -5080,8 +5178,8 @@
         <f>13*P36-O36-F36</f>
         <v>352.8</v>
       </c>
-      <c r="T36" s="5">
-        <f t="shared" si="19"/>
+      <c r="T36" s="27">
+        <f t="shared" si="20"/>
         <v>384</v>
       </c>
       <c r="U36" s="5"/>
@@ -5111,18 +5209,18 @@
       </c>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>246.95999999999998</v>
       </c>
       <c r="AF36" s="17">
         <v>8</v>
       </c>
       <c r="AG36" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>48</v>
       </c>
       <c r="AH36" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>268.79999999999995</v>
       </c>
       <c r="AI36" s="1">
@@ -5132,11 +5230,14 @@
         <v>84</v>
       </c>
       <c r="AK36" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="AL36" s="1"/>
-      <c r="AM36" s="1"/>
+      <c r="AM36" s="1">
+        <f t="shared" si="10"/>
+        <v>27.02</v>
+      </c>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
@@ -5205,8 +5306,8 @@
         <f>R37*$S$1</f>
         <v>555.07199999999989</v>
       </c>
-      <c r="T37" s="5">
-        <f t="shared" si="19"/>
+      <c r="T37" s="27">
+        <f t="shared" si="20"/>
         <v>576</v>
       </c>
       <c r="U37" s="5"/>
@@ -5236,18 +5337,18 @@
       </c>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>388.55039999999991</v>
       </c>
       <c r="AF37" s="17">
         <v>8</v>
       </c>
       <c r="AG37" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>72</v>
       </c>
       <c r="AH37" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>403.2</v>
       </c>
       <c r="AI37" s="1">
@@ -5257,11 +5358,14 @@
         <v>84</v>
       </c>
       <c r="AK37" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="AL37" s="1"/>
-      <c r="AM37" s="1"/>
+      <c r="AM37" s="1">
+        <f t="shared" si="10"/>
+        <v>51.24</v>
+      </c>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
@@ -5310,7 +5414,7 @@
         <v>207</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="24">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="25">E38-K38</f>
         <v>-20</v>
       </c>
       <c r="M38" s="1"/>
@@ -5327,11 +5431,11 @@
         <v>119.60000000000002</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>119.60000000000002</v>
       </c>
-      <c r="T38" s="5">
-        <f t="shared" si="19"/>
+      <c r="T38" s="27">
+        <f t="shared" si="20"/>
         <v>120</v>
       </c>
       <c r="U38" s="5"/>
@@ -5361,18 +5465,18 @@
       </c>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>83.720000000000013</v>
       </c>
       <c r="AF38" s="17">
         <v>10</v>
       </c>
       <c r="AG38" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12</v>
       </c>
       <c r="AH38" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="AI38" s="1">
@@ -5382,11 +5486,14 @@
         <v>84</v>
       </c>
       <c r="AK38" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL38" s="1"/>
-      <c r="AM38" s="1"/>
+      <c r="AM38" s="1">
+        <f t="shared" si="10"/>
+        <v>26.179999999999996</v>
+      </c>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
@@ -5435,7 +5542,7 @@
         <v>544</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-27</v>
       </c>
       <c r="M39" s="1"/>
@@ -5452,11 +5559,11 @@
         <v>640.80000000000007</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" ref="S39:S43" si="25">R39*$S$1</f>
+        <f t="shared" ref="S39:S43" si="26">R39*$S$1</f>
         <v>538.27200000000005</v>
       </c>
-      <c r="T39" s="5">
-        <f t="shared" si="19"/>
+      <c r="T39" s="27">
+        <f t="shared" si="20"/>
         <v>576</v>
       </c>
       <c r="U39" s="5"/>
@@ -5486,18 +5593,18 @@
       </c>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>376.79040000000003</v>
       </c>
       <c r="AF39" s="17">
         <v>8</v>
       </c>
       <c r="AG39" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>72</v>
       </c>
       <c r="AH39" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>403.2</v>
       </c>
       <c r="AI39" s="1">
@@ -5507,11 +5614,14 @@
         <v>84</v>
       </c>
       <c r="AK39" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="AL39" s="1"/>
-      <c r="AM39" s="1"/>
+      <c r="AM39" s="1">
+        <f t="shared" si="10"/>
+        <v>72.38</v>
+      </c>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
@@ -5560,7 +5670,7 @@
         <v>462</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-33</v>
       </c>
       <c r="M40" s="1"/>
@@ -5577,11 +5687,11 @@
         <v>702</v>
       </c>
       <c r="S40" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>589.67999999999995</v>
       </c>
-      <c r="T40" s="5">
-        <f t="shared" si="19"/>
+      <c r="T40" s="27">
+        <f t="shared" si="20"/>
         <v>576</v>
       </c>
       <c r="U40" s="5"/>
@@ -5611,18 +5721,18 @@
       </c>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>235.87199999999999</v>
       </c>
       <c r="AF40" s="17">
         <v>16</v>
       </c>
       <c r="AG40" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36</v>
       </c>
       <c r="AH40" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>230.4</v>
       </c>
       <c r="AI40" s="1">
@@ -5632,11 +5742,14 @@
         <v>84</v>
       </c>
       <c r="AK40" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL40" s="1"/>
-      <c r="AM40" s="1"/>
+      <c r="AM40" s="1">
+        <f t="shared" si="10"/>
+        <v>34.32</v>
+      </c>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
@@ -5685,7 +5798,7 @@
         <v>283</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-8</v>
       </c>
       <c r="M41" s="1"/>
@@ -5702,11 +5815,11 @@
         <v>522</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>438.47999999999996</v>
       </c>
-      <c r="T41" s="5">
-        <f t="shared" si="19"/>
+      <c r="T41" s="27">
+        <f t="shared" si="20"/>
         <v>480</v>
       </c>
       <c r="U41" s="5"/>
@@ -5736,18 +5849,18 @@
       </c>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>306.93599999999998</v>
       </c>
       <c r="AF41" s="17">
         <v>10</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>48</v>
       </c>
       <c r="AH41" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>336</v>
       </c>
       <c r="AI41" s="1">
@@ -5757,11 +5870,14 @@
         <v>84</v>
       </c>
       <c r="AK41" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="AL41" s="1"/>
-      <c r="AM41" s="1"/>
+      <c r="AM41" s="1">
+        <f t="shared" si="10"/>
+        <v>38.5</v>
+      </c>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
@@ -5810,7 +5926,7 @@
         <v>588</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-26</v>
       </c>
       <c r="M42" s="1"/>
@@ -5827,11 +5943,11 @@
         <v>958.60000000000014</v>
       </c>
       <c r="S42" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>805.22400000000005</v>
       </c>
-      <c r="T42" s="5">
-        <f t="shared" si="19"/>
+      <c r="T42" s="27">
+        <f t="shared" si="20"/>
         <v>840</v>
       </c>
       <c r="U42" s="5"/>
@@ -5863,18 +5979,18 @@
         <v>88</v>
       </c>
       <c r="AE42" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>563.65679999999998</v>
       </c>
       <c r="AF42" s="17">
         <v>10</v>
       </c>
       <c r="AG42" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84</v>
       </c>
       <c r="AH42" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>588</v>
       </c>
       <c r="AI42" s="1">
@@ -5884,11 +6000,14 @@
         <v>84</v>
       </c>
       <c r="AK42" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AL42" s="1"/>
-      <c r="AM42" s="1"/>
+      <c r="AM42" s="1">
+        <f t="shared" si="10"/>
+        <v>78.679999999999993</v>
+      </c>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
@@ -5937,7 +6056,7 @@
         <v>437</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-12</v>
       </c>
       <c r="M43" s="1"/>
@@ -5954,11 +6073,11 @@
         <v>530</v>
       </c>
       <c r="S43" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>445.2</v>
       </c>
-      <c r="T43" s="5">
-        <f t="shared" si="19"/>
+      <c r="T43" s="27">
+        <f t="shared" si="20"/>
         <v>420</v>
       </c>
       <c r="U43" s="5"/>
@@ -5988,18 +6107,18 @@
       </c>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>445.2</v>
       </c>
       <c r="AF43" s="17">
         <v>5</v>
       </c>
       <c r="AG43" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84</v>
       </c>
       <c r="AH43" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>420</v>
       </c>
       <c r="AI43" s="1">
@@ -6009,11 +6128,14 @@
         <v>144</v>
       </c>
       <c r="AK43" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.58333333333333337</v>
       </c>
       <c r="AL43" s="1"/>
-      <c r="AM43" s="1"/>
+      <c r="AM43" s="1">
+        <f t="shared" si="10"/>
+        <v>85</v>
+      </c>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
@@ -6062,7 +6184,7 @@
         <v>351</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-6</v>
       </c>
       <c r="M44" s="1"/>
@@ -6075,8 +6197,8 @@
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
-      <c r="T44" s="5">
-        <f t="shared" si="19"/>
+      <c r="T44" s="27">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U44" s="5"/>
@@ -6108,20 +6230,20 @@
         <v>88</v>
       </c>
       <c r="AE44" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF44" s="17">
         <v>16</v>
       </c>
       <c r="AG44" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AH44" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AH44" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AI44" s="1">
         <v>12</v>
       </c>
@@ -6129,11 +6251,14 @@
         <v>84</v>
       </c>
       <c r="AK44" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AL44" s="1"/>
-      <c r="AM44" s="1"/>
+      <c r="AM44" s="1">
+        <f t="shared" si="10"/>
+        <v>27.6</v>
+      </c>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
@@ -6182,7 +6307,7 @@
         <v>656</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-121</v>
       </c>
       <c r="M45" s="1"/>
@@ -6202,8 +6327,8 @@
         <f>R45*$S$1</f>
         <v>659.4</v>
       </c>
-      <c r="T45" s="5">
-        <f t="shared" si="19"/>
+      <c r="T45" s="27">
+        <f t="shared" si="20"/>
         <v>600</v>
       </c>
       <c r="U45" s="5"/>
@@ -6233,18 +6358,18 @@
       </c>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>461.57999999999993</v>
       </c>
       <c r="AF45" s="17">
         <v>10</v>
       </c>
       <c r="AG45" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
       <c r="AH45" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>420</v>
       </c>
       <c r="AI45" s="1">
@@ -6254,11 +6379,14 @@
         <v>84</v>
       </c>
       <c r="AK45" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="AL45" s="1"/>
-      <c r="AM45" s="1"/>
+      <c r="AM45" s="1">
+        <f t="shared" si="10"/>
+        <v>74.899999999999991</v>
+      </c>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
@@ -6307,7 +6435,7 @@
         <v>156</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-23</v>
       </c>
       <c r="M46" s="1"/>
@@ -6320,8 +6448,8 @@
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
-      <c r="T46" s="5">
-        <f t="shared" si="19"/>
+      <c r="T46" s="27">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U46" s="5"/>
@@ -6351,20 +6479,20 @@
       </c>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF46" s="17">
         <v>16</v>
       </c>
       <c r="AG46" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AH46" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AH46" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AI46" s="1">
         <v>12</v>
       </c>
@@ -6372,11 +6500,14 @@
         <v>84</v>
       </c>
       <c r="AK46" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AL46" s="1"/>
-      <c r="AM46" s="1"/>
+      <c r="AM46" s="1">
+        <f t="shared" si="10"/>
+        <v>10.64</v>
+      </c>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
@@ -6427,7 +6558,7 @@
         <v>876</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>129</v>
       </c>
       <c r="M47" s="1"/>
@@ -6444,11 +6575,11 @@
         <v>1056</v>
       </c>
       <c r="S47" s="5">
-        <f t="shared" ref="S47:S48" si="26">R47*$S$1</f>
+        <f t="shared" ref="S47:S48" si="27">R47*$S$1</f>
         <v>887.04</v>
       </c>
-      <c r="T47" s="5">
-        <f t="shared" si="19"/>
+      <c r="T47" s="27">
+        <f t="shared" si="20"/>
         <v>840</v>
       </c>
       <c r="U47" s="5"/>
@@ -6478,18 +6609,18 @@
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>620.92799999999988</v>
       </c>
       <c r="AF47" s="17">
         <v>10</v>
       </c>
       <c r="AG47" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84</v>
       </c>
       <c r="AH47" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>588</v>
       </c>
       <c r="AI47" s="1">
@@ -6499,11 +6630,14 @@
         <v>84</v>
       </c>
       <c r="AK47" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AL47" s="1"/>
-      <c r="AM47" s="1"/>
+      <c r="AM47" s="1">
+        <f t="shared" si="10"/>
+        <v>140.69999999999999</v>
+      </c>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -6552,7 +6686,7 @@
         <v>755</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-38</v>
       </c>
       <c r="M48" s="1"/>
@@ -6569,11 +6703,11 @@
         <v>796.60000000000014</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>669.14400000000012</v>
       </c>
-      <c r="T48" s="5">
-        <f t="shared" si="19"/>
+      <c r="T48" s="27">
+        <f t="shared" si="20"/>
         <v>660</v>
       </c>
       <c r="U48" s="5"/>
@@ -6603,18 +6737,18 @@
       </c>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>669.14400000000012</v>
       </c>
       <c r="AF48" s="17">
         <v>5</v>
       </c>
       <c r="AG48" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>132</v>
       </c>
       <c r="AH48" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>660</v>
       </c>
       <c r="AI48" s="1">
@@ -6624,11 +6758,14 @@
         <v>84</v>
       </c>
       <c r="AK48" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="AL48" s="1"/>
-      <c r="AM48" s="1"/>
+      <c r="AM48" s="1">
+        <f t="shared" si="10"/>
+        <v>143.4</v>
+      </c>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -6677,7 +6814,7 @@
         <v>37</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M49" s="1"/>
@@ -6690,8 +6827,8 @@
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
-      <c r="T49" s="5">
-        <f t="shared" si="19"/>
+      <c r="T49" s="27">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U49" s="5"/>
@@ -6723,20 +6860,20 @@
         <v>164</v>
       </c>
       <c r="AE49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF49" s="17">
         <v>8</v>
       </c>
       <c r="AG49" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AH49" s="1">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AH49" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AI49" s="1">
         <v>12</v>
       </c>
@@ -6744,11 +6881,14 @@
         <v>84</v>
       </c>
       <c r="AK49" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AL49" s="1"/>
-      <c r="AM49" s="1"/>
+      <c r="AM49" s="1">
+        <f t="shared" si="10"/>
+        <v>6.66</v>
+      </c>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
@@ -6791,7 +6931,7 @@
         <v>72</v>
       </c>
       <c r="L50" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-24</v>
       </c>
       <c r="M50" s="11"/>
@@ -6804,7 +6944,7 @@
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
       <c r="S50" s="13"/>
-      <c r="T50" s="13"/>
+      <c r="T50" s="26"/>
       <c r="U50" s="13"/>
       <c r="V50" s="11"/>
       <c r="W50" s="11">
@@ -6839,7 +6979,10 @@
       <c r="AJ50" s="11"/>
       <c r="AK50" s="11"/>
       <c r="AL50" s="1"/>
-      <c r="AM50" s="1"/>
+      <c r="AM50" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
@@ -6888,7 +7031,7 @@
         <v>300</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-5</v>
       </c>
       <c r="M51" s="1"/>
@@ -6908,8 +7051,8 @@
         <f>R51*$S$1</f>
         <v>425.88</v>
       </c>
-      <c r="T51" s="5">
-        <f t="shared" ref="T51:T68" si="27">AF51*AG51</f>
+      <c r="T51" s="27">
+        <f t="shared" ref="T51:T68" si="28">AF51*AG51</f>
         <v>420</v>
       </c>
       <c r="U51" s="5"/>
@@ -6939,18 +7082,18 @@
       </c>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1">
-        <f t="shared" ref="AE51:AE68" si="28">G51*S51</f>
+        <f t="shared" ref="AE51:AE68" si="29">G51*S51</f>
         <v>425.88</v>
       </c>
       <c r="AF51" s="17">
         <v>5</v>
       </c>
       <c r="AG51" s="1">
-        <f t="shared" ref="AG51:AG68" si="29">MROUND(S51, AF51*AI51)/AF51</f>
+        <f t="shared" ref="AG51:AG68" si="30">MROUND(S51, AF51*AI51)/AF51</f>
         <v>84</v>
       </c>
       <c r="AH51" s="1">
-        <f t="shared" ref="AH51:AH68" si="30">AG51*AF51*G51</f>
+        <f t="shared" ref="AH51:AH68" si="31">AG51*AF51*G51</f>
         <v>420</v>
       </c>
       <c r="AI51" s="1">
@@ -6960,11 +7103,14 @@
         <v>144</v>
       </c>
       <c r="AK51" s="17">
-        <f t="shared" ref="AK51:AK68" si="31">AG51/AJ51</f>
+        <f t="shared" ref="AK51:AK68" si="32">AG51/AJ51</f>
         <v>0.58333333333333337</v>
       </c>
       <c r="AL51" s="1"/>
-      <c r="AM51" s="1"/>
+      <c r="AM51" s="1">
+        <f t="shared" si="10"/>
+        <v>59</v>
+      </c>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
@@ -7011,7 +7157,7 @@
         <v>31</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M52" s="1"/>
@@ -7024,8 +7170,8 @@
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
-      <c r="T52" s="5">
-        <f t="shared" si="27"/>
+      <c r="T52" s="27">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U52" s="5"/>
@@ -7055,20 +7201,20 @@
       </c>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF52" s="17">
         <v>5</v>
       </c>
       <c r="AG52" s="1">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AH52" s="1">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="AH52" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="AI52" s="1">
         <v>12</v>
       </c>
@@ -7076,11 +7222,14 @@
         <v>84</v>
       </c>
       <c r="AK52" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AL52" s="1"/>
-      <c r="AM52" s="1"/>
+      <c r="AM52" s="1">
+        <f t="shared" si="10"/>
+        <v>6.2</v>
+      </c>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
@@ -7130,7 +7279,7 @@
         <v>151.5</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M53" s="1"/>
@@ -7147,11 +7296,11 @@
         <v>98.300000000000011</v>
       </c>
       <c r="S53" s="5">
-        <f t="shared" ref="S53:S68" si="32">14*P53-O53-F53</f>
+        <f t="shared" ref="S53:S68" si="33">14*P53-O53-F53</f>
         <v>98.300000000000011</v>
       </c>
-      <c r="T53" s="5">
-        <f t="shared" si="27"/>
+      <c r="T53" s="27">
+        <f t="shared" si="28"/>
         <v>103.60000000000001</v>
       </c>
       <c r="U53" s="5"/>
@@ -7181,18 +7330,18 @@
       </c>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>98.300000000000011</v>
       </c>
       <c r="AF53" s="17">
         <v>3.7</v>
       </c>
       <c r="AG53" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>28</v>
       </c>
       <c r="AH53" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>103.60000000000001</v>
       </c>
       <c r="AI53" s="1">
@@ -7202,11 +7351,14 @@
         <v>126</v>
       </c>
       <c r="AK53" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="AL53" s="1"/>
-      <c r="AM53" s="1"/>
+      <c r="AM53" s="1">
+        <f t="shared" si="10"/>
+        <v>30.3</v>
+      </c>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
@@ -7255,7 +7407,7 @@
         <v>623</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-22</v>
       </c>
       <c r="M54" s="1"/>
@@ -7275,8 +7427,8 @@
         <f>U54</f>
         <v>1800</v>
       </c>
-      <c r="T54" s="5">
-        <f t="shared" si="27"/>
+      <c r="T54" s="27">
+        <f t="shared" si="28"/>
         <v>1764</v>
       </c>
       <c r="U54" s="21">
@@ -7312,18 +7464,18 @@
         <v>168</v>
       </c>
       <c r="AE54" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>414</v>
       </c>
       <c r="AF54" s="17">
         <v>6</v>
       </c>
       <c r="AG54" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>294</v>
       </c>
       <c r="AH54" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>405.72</v>
       </c>
       <c r="AI54" s="1">
@@ -7333,11 +7485,14 @@
         <v>140</v>
       </c>
       <c r="AK54" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>2.1</v>
       </c>
       <c r="AL54" s="1"/>
-      <c r="AM54" s="1"/>
+      <c r="AM54" s="1">
+        <f t="shared" si="10"/>
+        <v>27.646000000000001</v>
+      </c>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
@@ -7386,7 +7541,7 @@
         <v>765</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-104</v>
       </c>
       <c r="M55" s="1"/>
@@ -7399,8 +7554,8 @@
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
-      <c r="T55" s="5">
-        <f t="shared" si="27"/>
+      <c r="T55" s="27">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U55" s="5"/>
@@ -7430,20 +7585,20 @@
       </c>
       <c r="AD55" s="1"/>
       <c r="AE55" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF55" s="17">
         <v>12</v>
       </c>
       <c r="AG55" s="1">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AH55" s="1">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="AH55" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="AI55" s="1">
         <v>14</v>
       </c>
@@ -7451,11 +7606,14 @@
         <v>70</v>
       </c>
       <c r="AK55" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AL55" s="1"/>
-      <c r="AM55" s="1"/>
+      <c r="AM55" s="1">
+        <f t="shared" si="10"/>
+        <v>33.049999999999997</v>
+      </c>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
@@ -7504,7 +7662,7 @@
         <v>764</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-30</v>
       </c>
       <c r="M56" s="1"/>
@@ -7524,8 +7682,8 @@
         <f>R56*$S$1</f>
         <v>808.58400000000006</v>
       </c>
-      <c r="T56" s="5">
-        <f t="shared" si="27"/>
+      <c r="T56" s="27">
+        <f t="shared" si="28"/>
         <v>840</v>
       </c>
       <c r="U56" s="5"/>
@@ -7555,18 +7713,18 @@
       </c>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>202.14600000000002</v>
       </c>
       <c r="AF56" s="17">
         <v>12</v>
       </c>
       <c r="AG56" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>70</v>
       </c>
       <c r="AH56" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>210</v>
       </c>
       <c r="AI56" s="1">
@@ -7576,11 +7734,14 @@
         <v>70</v>
       </c>
       <c r="AK56" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="AL56" s="1"/>
-      <c r="AM56" s="1"/>
+      <c r="AM56" s="1">
+        <f t="shared" si="10"/>
+        <v>36.700000000000003</v>
+      </c>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
@@ -7629,7 +7790,7 @@
         <v>101</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-5</v>
       </c>
       <c r="M57" s="1"/>
@@ -7642,8 +7803,8 @@
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
-      <c r="T57" s="5">
-        <f t="shared" si="27"/>
+      <c r="T57" s="27">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U57" s="5"/>
@@ -7675,20 +7836,20 @@
         <v>164</v>
       </c>
       <c r="AE57" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF57" s="17">
         <v>6</v>
       </c>
       <c r="AG57" s="1">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AH57" s="1">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="AH57" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="AI57" s="1">
         <v>14</v>
       </c>
@@ -7696,11 +7857,14 @@
         <v>140</v>
       </c>
       <c r="AK57" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AL57" s="1"/>
-      <c r="AM57" s="1"/>
+      <c r="AM57" s="1">
+        <f t="shared" si="10"/>
+        <v>3.456</v>
+      </c>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
@@ -7749,7 +7913,7 @@
         <v>348</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-17</v>
       </c>
       <c r="M58" s="1"/>
@@ -7766,11 +7930,11 @@
         <v>340.80000000000007</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>340.80000000000007</v>
       </c>
-      <c r="T58" s="5">
-        <f t="shared" si="27"/>
+      <c r="T58" s="27">
+        <f t="shared" si="28"/>
         <v>336</v>
       </c>
       <c r="U58" s="5"/>
@@ -7800,18 +7964,18 @@
       </c>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>61.344000000000008</v>
       </c>
       <c r="AF58" s="17">
         <v>6</v>
       </c>
       <c r="AG58" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>56</v>
       </c>
       <c r="AH58" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>60.48</v>
       </c>
       <c r="AI58" s="1">
@@ -7821,11 +7985,14 @@
         <v>140</v>
       </c>
       <c r="AK58" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.4</v>
       </c>
       <c r="AL58" s="1"/>
-      <c r="AM58" s="1"/>
+      <c r="AM58" s="1">
+        <f t="shared" si="10"/>
+        <v>11.916</v>
+      </c>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
@@ -7872,7 +8039,7 @@
         <v>11</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M59" s="1"/>
@@ -7885,8 +8052,8 @@
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
       <c r="S59" s="5"/>
-      <c r="T59" s="5">
-        <f t="shared" si="27"/>
+      <c r="T59" s="27">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U59" s="5"/>
@@ -7918,20 +8085,20 @@
         <v>164</v>
       </c>
       <c r="AE59" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF59" s="17">
         <v>6</v>
       </c>
       <c r="AG59" s="1">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AH59" s="1">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="AH59" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="AI59" s="1">
         <v>14</v>
       </c>
@@ -7939,11 +8106,14 @@
         <v>70</v>
       </c>
       <c r="AK59" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AL59" s="1"/>
-      <c r="AM59" s="1"/>
+      <c r="AM59" s="1">
+        <f t="shared" si="10"/>
+        <v>0.39600000000000002</v>
+      </c>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
@@ -7992,7 +8162,7 @@
         <v>805</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-9</v>
       </c>
       <c r="M60" s="1"/>
@@ -8011,11 +8181,11 @@
         <v>1002.7999999999997</v>
       </c>
       <c r="S60" s="5">
-        <f t="shared" ref="S60:S62" si="33">R60*$S$1</f>
+        <f t="shared" ref="S60:S62" si="34">R60*$S$1</f>
         <v>842.35199999999975</v>
       </c>
-      <c r="T60" s="5">
-        <f t="shared" si="27"/>
+      <c r="T60" s="27">
+        <f t="shared" si="28"/>
         <v>840</v>
       </c>
       <c r="U60" s="5"/>
@@ -8045,18 +8215,18 @@
       </c>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>252.70559999999992</v>
       </c>
       <c r="AF60" s="17">
         <v>12</v>
       </c>
       <c r="AG60" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>70</v>
       </c>
       <c r="AH60" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>252</v>
       </c>
       <c r="AI60" s="1">
@@ -8066,11 +8236,14 @@
         <v>70</v>
       </c>
       <c r="AK60" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="AL60" s="1"/>
-      <c r="AM60" s="1"/>
+      <c r="AM60" s="1">
+        <f t="shared" si="10"/>
+        <v>47.76</v>
+      </c>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
@@ -8119,7 +8292,7 @@
         <v>564</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-2</v>
       </c>
       <c r="M61" s="1"/>
@@ -8136,11 +8309,11 @@
         <v>632.60000000000014</v>
       </c>
       <c r="S61" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>531.38400000000013</v>
       </c>
-      <c r="T61" s="5">
-        <f t="shared" si="27"/>
+      <c r="T61" s="27">
+        <f t="shared" si="28"/>
         <v>504</v>
       </c>
       <c r="U61" s="5"/>
@@ -8170,18 +8343,18 @@
       </c>
       <c r="AD61" s="1"/>
       <c r="AE61" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>159.41520000000003</v>
       </c>
       <c r="AF61" s="17">
         <v>12</v>
       </c>
       <c r="AG61" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>42</v>
       </c>
       <c r="AH61" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>151.19999999999999</v>
       </c>
       <c r="AI61" s="1">
@@ -8191,11 +8364,14 @@
         <v>70</v>
       </c>
       <c r="AK61" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.6</v>
       </c>
       <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
+      <c r="AM61" s="1">
+        <f t="shared" si="10"/>
+        <v>33.72</v>
+      </c>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
@@ -8244,7 +8420,7 @@
         <v>537</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-10</v>
       </c>
       <c r="M62" s="1"/>
@@ -8263,11 +8439,11 @@
         <v>1000</v>
       </c>
       <c r="S62" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>840</v>
       </c>
-      <c r="T62" s="5">
-        <f t="shared" si="27"/>
+      <c r="T62" s="27">
+        <f t="shared" si="28"/>
         <v>784</v>
       </c>
       <c r="U62" s="21">
@@ -8301,18 +8477,18 @@
       </c>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>252</v>
       </c>
       <c r="AF62" s="17">
         <v>14</v>
       </c>
       <c r="AG62" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>56</v>
       </c>
       <c r="AH62" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>235.2</v>
       </c>
       <c r="AI62" s="1">
@@ -8322,11 +8498,14 @@
         <v>70</v>
       </c>
       <c r="AK62" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.8</v>
       </c>
       <c r="AL62" s="1"/>
-      <c r="AM62" s="1"/>
+      <c r="AM62" s="1">
+        <f t="shared" si="10"/>
+        <v>31.62</v>
+      </c>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
@@ -8375,7 +8554,7 @@
         <v>1417</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-335</v>
       </c>
       <c r="M63" s="1"/>
@@ -8394,11 +8573,11 @@
         <v>2500</v>
       </c>
       <c r="S63" s="5">
-        <f t="shared" ref="S63" si="34">U63</f>
+        <f t="shared" ref="S63" si="35">U63</f>
         <v>2500</v>
       </c>
-      <c r="T63" s="5">
-        <f t="shared" si="27"/>
+      <c r="T63" s="27">
+        <f t="shared" si="28"/>
         <v>2520</v>
       </c>
       <c r="U63" s="21">
@@ -8434,18 +8613,18 @@
         <v>167</v>
       </c>
       <c r="AE63" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>625</v>
       </c>
       <c r="AF63" s="17">
         <v>12</v>
       </c>
       <c r="AG63" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>210</v>
       </c>
       <c r="AH63" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>630</v>
       </c>
       <c r="AI63" s="1">
@@ -8455,11 +8634,14 @@
         <v>70</v>
       </c>
       <c r="AK63" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3</v>
       </c>
       <c r="AL63" s="1"/>
-      <c r="AM63" s="1"/>
+      <c r="AM63" s="1">
+        <f t="shared" si="10"/>
+        <v>54.1</v>
+      </c>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
@@ -8510,7 +8692,7 @@
         <v>1311</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-456</v>
       </c>
       <c r="M64" s="1"/>
@@ -8525,8 +8707,8 @@
       <c r="Q64" s="5"/>
       <c r="R64" s="5"/>
       <c r="S64" s="5"/>
-      <c r="T64" s="5">
-        <f t="shared" si="27"/>
+      <c r="T64" s="27">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U64" s="5"/>
@@ -8556,20 +8738,20 @@
       </c>
       <c r="AD64" s="1"/>
       <c r="AE64" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF64" s="17">
         <v>12</v>
       </c>
       <c r="AG64" s="1">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AH64" s="1">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="AH64" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="AI64" s="1">
         <v>14</v>
       </c>
@@ -8577,11 +8759,14 @@
         <v>70</v>
       </c>
       <c r="AK64" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AL64" s="1"/>
-      <c r="AM64" s="1"/>
+      <c r="AM64" s="1">
+        <f t="shared" si="10"/>
+        <v>42.75</v>
+      </c>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
@@ -8630,7 +8815,7 @@
         <v>418</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-23</v>
       </c>
       <c r="M65" s="1"/>
@@ -8649,11 +8834,11 @@
         <v>718</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" ref="S65:S66" si="35">R65*$S$1</f>
+        <f t="shared" ref="S65:S66" si="36">R65*$S$1</f>
         <v>603.12</v>
       </c>
-      <c r="T65" s="5">
-        <f t="shared" si="27"/>
+      <c r="T65" s="27">
+        <f t="shared" si="28"/>
         <v>588</v>
       </c>
       <c r="U65" s="5"/>
@@ -8683,18 +8868,18 @@
       </c>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>120.62400000000001</v>
       </c>
       <c r="AF65" s="17">
         <v>6</v>
       </c>
       <c r="AG65" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>98</v>
       </c>
       <c r="AH65" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>117.60000000000001</v>
       </c>
       <c r="AI65" s="1">
@@ -8704,11 +8889,14 @@
         <v>140</v>
       </c>
       <c r="AK65" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.7</v>
       </c>
       <c r="AL65" s="1"/>
-      <c r="AM65" s="1"/>
+      <c r="AM65" s="1">
+        <f t="shared" si="10"/>
+        <v>15.8</v>
+      </c>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
@@ -8757,7 +8945,7 @@
         <v>800</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-34</v>
       </c>
       <c r="M66" s="1"/>
@@ -8776,11 +8964,11 @@
         <v>2000</v>
       </c>
       <c r="S66" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1680</v>
       </c>
-      <c r="T66" s="5">
-        <f t="shared" si="27"/>
+      <c r="T66" s="27">
+        <f t="shared" si="28"/>
         <v>1680</v>
       </c>
       <c r="U66" s="21">
@@ -8814,18 +9002,18 @@
       </c>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>386.40000000000003</v>
       </c>
       <c r="AF66" s="17">
         <v>6</v>
       </c>
       <c r="AG66" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>280</v>
       </c>
       <c r="AH66" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>386.40000000000003</v>
       </c>
       <c r="AI66" s="1">
@@ -8835,11 +9023,14 @@
         <v>140</v>
       </c>
       <c r="AK66" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>2</v>
       </c>
       <c r="AL66" s="1"/>
-      <c r="AM66" s="1"/>
+      <c r="AM66" s="1">
+        <f t="shared" si="10"/>
+        <v>35.235999999999997</v>
+      </c>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
@@ -8886,7 +9077,7 @@
         <v>39.700000000000003</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-5</v>
       </c>
       <c r="M67" s="1"/>
@@ -8903,11 +9094,11 @@
         <v>34.260000000000012</v>
       </c>
       <c r="S67" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>34.260000000000012</v>
       </c>
-      <c r="T67" s="5">
-        <f t="shared" si="27"/>
+      <c r="T67" s="27">
+        <f t="shared" si="28"/>
         <v>37.800000000000004</v>
       </c>
       <c r="U67" s="5"/>
@@ -8937,18 +9128,18 @@
       </c>
       <c r="AD67" s="1"/>
       <c r="AE67" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>34.260000000000012</v>
       </c>
       <c r="AF67" s="17">
         <v>2.7</v>
       </c>
       <c r="AG67" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14</v>
       </c>
       <c r="AH67" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>37.800000000000004</v>
       </c>
       <c r="AI67" s="1">
@@ -8958,11 +9149,14 @@
         <v>126</v>
       </c>
       <c r="AK67" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="AL67" s="1"/>
-      <c r="AM67" s="1"/>
+      <c r="AM67" s="1">
+        <f t="shared" si="10"/>
+        <v>6.94</v>
+      </c>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
@@ -9013,7 +9207,7 @@
         <v>233</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>159.69999999999999</v>
       </c>
       <c r="M68" s="1"/>
@@ -9032,11 +9226,11 @@
         <v>254.95999999999992</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>254.95999999999992</v>
       </c>
-      <c r="T68" s="5">
-        <f t="shared" si="27"/>
+      <c r="T68" s="27">
+        <f t="shared" si="28"/>
         <v>240</v>
       </c>
       <c r="U68" s="5"/>
@@ -9066,18 +9260,18 @@
       </c>
       <c r="AD68" s="1"/>
       <c r="AE68" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>254.95999999999992</v>
       </c>
       <c r="AF68" s="17">
         <v>5</v>
       </c>
       <c r="AG68" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>48</v>
       </c>
       <c r="AH68" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>240</v>
       </c>
       <c r="AI68" s="1">
@@ -9087,11 +9281,14 @@
         <v>84</v>
       </c>
       <c r="AK68" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="AL68" s="1"/>
-      <c r="AM68" s="1"/>
+      <c r="AM68" s="1">
+        <f t="shared" si="10"/>
+        <v>78.539999999999992</v>
+      </c>
       <c r="AN68" s="1"/>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
@@ -9140,7 +9337,7 @@
         <v>162.69999999999999</v>
       </c>
       <c r="L69" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M69" s="11"/>
@@ -9153,7 +9350,7 @@
       <c r="Q69" s="13"/>
       <c r="R69" s="13"/>
       <c r="S69" s="13"/>
-      <c r="T69" s="13"/>
+      <c r="T69" s="26"/>
       <c r="U69" s="13"/>
       <c r="V69" s="11"/>
       <c r="W69" s="11">
@@ -9224,7 +9421,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
+      <c r="T70" s="24"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
@@ -9279,7 +9476,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
+      <c r="T71" s="24"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
@@ -9334,7 +9531,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
+      <c r="T72" s="24"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
@@ -9389,7 +9586,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
+      <c r="T73" s="24"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
@@ -9444,7 +9641,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
-      <c r="T74" s="1"/>
+      <c r="T74" s="24"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
@@ -9499,7 +9696,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
+      <c r="T75" s="24"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
@@ -9554,7 +9751,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
+      <c r="T76" s="24"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
@@ -9609,7 +9806,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
+      <c r="T77" s="24"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
@@ -9664,7 +9861,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
+      <c r="T78" s="24"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
@@ -9719,7 +9916,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
+      <c r="T79" s="24"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
@@ -9774,7 +9971,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
+      <c r="T80" s="24"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
@@ -9829,7 +10026,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
+      <c r="T81" s="24"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
@@ -9884,7 +10081,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
-      <c r="T82" s="1"/>
+      <c r="T82" s="24"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
@@ -9939,7 +10136,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
-      <c r="T83" s="1"/>
+      <c r="T83" s="24"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
@@ -9994,7 +10191,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
-      <c r="T84" s="1"/>
+      <c r="T84" s="24"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
@@ -10049,7 +10246,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
-      <c r="T85" s="1"/>
+      <c r="T85" s="24"/>
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
@@ -10104,7 +10301,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
-      <c r="T86" s="1"/>
+      <c r="T86" s="24"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
@@ -10159,7 +10356,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
-      <c r="T87" s="1"/>
+      <c r="T87" s="24"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
@@ -10214,7 +10411,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
-      <c r="T88" s="1"/>
+      <c r="T88" s="24"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
@@ -10269,7 +10466,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
-      <c r="T89" s="1"/>
+      <c r="T89" s="24"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
@@ -10324,7 +10521,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
+      <c r="T90" s="24"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
@@ -10379,7 +10576,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
+      <c r="T91" s="24"/>
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
@@ -10434,7 +10631,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
+      <c r="T92" s="24"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
@@ -10489,7 +10686,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
-      <c r="T93" s="1"/>
+      <c r="T93" s="24"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
@@ -10544,7 +10741,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
-      <c r="T94" s="1"/>
+      <c r="T94" s="24"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
@@ -10599,7 +10796,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
-      <c r="T95" s="1"/>
+      <c r="T95" s="24"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
@@ -10654,7 +10851,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
-      <c r="T96" s="1"/>
+      <c r="T96" s="24"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
@@ -10709,7 +10906,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
-      <c r="T97" s="1"/>
+      <c r="T97" s="24"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
@@ -10764,7 +10961,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
-      <c r="T98" s="1"/>
+      <c r="T98" s="24"/>
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
@@ -10819,7 +11016,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
-      <c r="T99" s="1"/>
+      <c r="T99" s="24"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
@@ -10874,7 +11071,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
-      <c r="T100" s="1"/>
+      <c r="T100" s="24"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
@@ -10929,7 +11126,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
-      <c r="T101" s="1"/>
+      <c r="T101" s="24"/>
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
@@ -10984,7 +11181,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
-      <c r="T102" s="1"/>
+      <c r="T102" s="24"/>
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
@@ -11039,7 +11236,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
-      <c r="T103" s="1"/>
+      <c r="T103" s="24"/>
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
@@ -11094,7 +11291,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
-      <c r="T104" s="1"/>
+      <c r="T104" s="24"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
@@ -11149,7 +11346,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
-      <c r="T105" s="1"/>
+      <c r="T105" s="24"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
@@ -11204,7 +11401,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
-      <c r="T106" s="1"/>
+      <c r="T106" s="24"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
@@ -11259,7 +11456,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
-      <c r="T107" s="1"/>
+      <c r="T107" s="24"/>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
@@ -11314,7 +11511,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
+      <c r="T108" s="24"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
@@ -11369,7 +11566,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
-      <c r="T109" s="1"/>
+      <c r="T109" s="24"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
@@ -11424,7 +11621,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
-      <c r="T110" s="1"/>
+      <c r="T110" s="24"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
@@ -11479,7 +11676,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
-      <c r="T111" s="1"/>
+      <c r="T111" s="24"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
@@ -11534,7 +11731,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
-      <c r="T112" s="1"/>
+      <c r="T112" s="24"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
@@ -11589,7 +11786,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
-      <c r="T113" s="1"/>
+      <c r="T113" s="24"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
@@ -11644,7 +11841,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
-      <c r="T114" s="1"/>
+      <c r="T114" s="24"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
@@ -11699,7 +11896,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
-      <c r="T115" s="1"/>
+      <c r="T115" s="24"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
@@ -11754,7 +11951,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
-      <c r="T116" s="1"/>
+      <c r="T116" s="24"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
@@ -11809,7 +12006,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
-      <c r="T117" s="1"/>
+      <c r="T117" s="24"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
@@ -11864,7 +12061,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
-      <c r="T118" s="1"/>
+      <c r="T118" s="24"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
@@ -11919,7 +12116,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
-      <c r="T119" s="1"/>
+      <c r="T119" s="24"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
@@ -11974,7 +12171,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
-      <c r="T120" s="1"/>
+      <c r="T120" s="24"/>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
@@ -12029,7 +12226,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
-      <c r="T121" s="1"/>
+      <c r="T121" s="24"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
@@ -12084,7 +12281,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
+      <c r="T122" s="24"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
@@ -12139,7 +12336,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
+      <c r="T123" s="24"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
@@ -12194,7 +12391,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
+      <c r="T124" s="24"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
@@ -12249,7 +12446,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
+      <c r="T125" s="24"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
@@ -12304,7 +12501,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
+      <c r="T126" s="24"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
@@ -12359,7 +12556,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
-      <c r="T127" s="1"/>
+      <c r="T127" s="24"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
@@ -12414,7 +12611,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
-      <c r="T128" s="1"/>
+      <c r="T128" s="24"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
@@ -12469,7 +12666,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
-      <c r="T129" s="1"/>
+      <c r="T129" s="24"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
@@ -12524,7 +12721,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
+      <c r="T130" s="24"/>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
@@ -12579,7 +12776,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
+      <c r="T131" s="24"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
@@ -12634,7 +12831,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
-      <c r="T132" s="1"/>
+      <c r="T132" s="24"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
@@ -12689,7 +12886,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
+      <c r="T133" s="24"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
@@ -12744,7 +12941,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
+      <c r="T134" s="24"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
@@ -12799,7 +12996,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
-      <c r="T135" s="1"/>
+      <c r="T135" s="24"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
@@ -12854,7 +13051,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
-      <c r="T136" s="1"/>
+      <c r="T136" s="24"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
@@ -12909,7 +13106,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
-      <c r="T137" s="1"/>
+      <c r="T137" s="24"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
@@ -12964,7 +13161,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
-      <c r="T138" s="1"/>
+      <c r="T138" s="24"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
@@ -13019,7 +13216,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
+      <c r="T139" s="24"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
@@ -13074,7 +13271,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
+      <c r="T140" s="24"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
@@ -13129,7 +13326,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
-      <c r="T141" s="1"/>
+      <c r="T141" s="24"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
@@ -13184,7 +13381,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
-      <c r="T142" s="1"/>
+      <c r="T142" s="24"/>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
@@ -13239,7 +13436,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
-      <c r="T143" s="1"/>
+      <c r="T143" s="24"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
@@ -13294,7 +13491,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
+      <c r="T144" s="24"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
@@ -13349,7 +13546,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
-      <c r="T145" s="1"/>
+      <c r="T145" s="24"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
@@ -13404,7 +13601,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
-      <c r="T146" s="1"/>
+      <c r="T146" s="24"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
@@ -13459,7 +13656,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
-      <c r="T147" s="1"/>
+      <c r="T147" s="24"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
@@ -13514,7 +13711,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
-      <c r="T148" s="1"/>
+      <c r="T148" s="24"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
@@ -13569,7 +13766,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
-      <c r="T149" s="1"/>
+      <c r="T149" s="24"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
@@ -13624,7 +13821,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
+      <c r="T150" s="24"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
@@ -13679,7 +13876,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
-      <c r="T151" s="1"/>
+      <c r="T151" s="24"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
@@ -13734,7 +13931,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
+      <c r="T152" s="24"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -13789,7 +13986,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
+      <c r="T153" s="24"/>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
@@ -13844,7 +14041,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
-      <c r="T154" s="1"/>
+      <c r="T154" s="24"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
@@ -13899,7 +14096,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
-      <c r="T155" s="1"/>
+      <c r="T155" s="24"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
@@ -13954,7 +14151,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
-      <c r="T156" s="1"/>
+      <c r="T156" s="24"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
@@ -14009,7 +14206,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
-      <c r="T157" s="1"/>
+      <c r="T157" s="24"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
@@ -14064,7 +14261,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
-      <c r="T158" s="1"/>
+      <c r="T158" s="24"/>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
@@ -14119,7 +14316,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
-      <c r="T159" s="1"/>
+      <c r="T159" s="24"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
@@ -14174,7 +14371,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
-      <c r="T160" s="1"/>
+      <c r="T160" s="24"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
@@ -14229,7 +14426,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
-      <c r="T161" s="1"/>
+      <c r="T161" s="24"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
@@ -14284,7 +14481,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
-      <c r="T162" s="1"/>
+      <c r="T162" s="24"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
@@ -14339,7 +14536,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
-      <c r="T163" s="1"/>
+      <c r="T163" s="24"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
@@ -14394,7 +14591,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
-      <c r="T164" s="1"/>
+      <c r="T164" s="24"/>
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
@@ -14449,7 +14646,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
-      <c r="T165" s="1"/>
+      <c r="T165" s="24"/>
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
@@ -14504,7 +14701,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
-      <c r="T166" s="1"/>
+      <c r="T166" s="24"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
@@ -14559,7 +14756,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
-      <c r="T167" s="1"/>
+      <c r="T167" s="24"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
@@ -14614,7 +14811,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
-      <c r="T168" s="1"/>
+      <c r="T168" s="24"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
@@ -14669,7 +14866,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
-      <c r="T169" s="1"/>
+      <c r="T169" s="24"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
@@ -14724,7 +14921,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
-      <c r="T170" s="1"/>
+      <c r="T170" s="24"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
@@ -14779,7 +14976,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
-      <c r="T171" s="1"/>
+      <c r="T171" s="24"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
@@ -14834,7 +15031,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
-      <c r="T172" s="1"/>
+      <c r="T172" s="24"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
@@ -14889,7 +15086,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
-      <c r="T173" s="1"/>
+      <c r="T173" s="24"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
@@ -14944,7 +15141,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
-      <c r="T174" s="1"/>
+      <c r="T174" s="24"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
@@ -14999,7 +15196,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
-      <c r="T175" s="1"/>
+      <c r="T175" s="24"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
@@ -15054,7 +15251,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
-      <c r="T176" s="1"/>
+      <c r="T176" s="24"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
@@ -15109,7 +15306,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
-      <c r="T177" s="1"/>
+      <c r="T177" s="24"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
@@ -15164,7 +15361,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
-      <c r="T178" s="1"/>
+      <c r="T178" s="24"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
@@ -15219,7 +15416,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
-      <c r="T179" s="1"/>
+      <c r="T179" s="24"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
@@ -15274,7 +15471,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
+      <c r="T180" s="24"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
@@ -15329,7 +15526,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
-      <c r="T181" s="1"/>
+      <c r="T181" s="24"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
@@ -15384,7 +15581,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
-      <c r="T182" s="1"/>
+      <c r="T182" s="24"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
@@ -15439,7 +15636,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
-      <c r="T183" s="1"/>
+      <c r="T183" s="24"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
@@ -15494,7 +15691,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
-      <c r="T184" s="1"/>
+      <c r="T184" s="24"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
@@ -15549,7 +15746,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
-      <c r="T185" s="1"/>
+      <c r="T185" s="24"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
@@ -15604,7 +15801,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
-      <c r="T186" s="1"/>
+      <c r="T186" s="24"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
@@ -15659,7 +15856,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
-      <c r="T187" s="1"/>
+      <c r="T187" s="24"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
@@ -15714,7 +15911,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
-      <c r="T188" s="1"/>
+      <c r="T188" s="24"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
@@ -15769,7 +15966,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
+      <c r="T189" s="24"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
@@ -15824,7 +16021,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
-      <c r="T190" s="1"/>
+      <c r="T190" s="24"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
@@ -15879,7 +16076,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
-      <c r="T191" s="1"/>
+      <c r="T191" s="24"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
@@ -15934,7 +16131,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
-      <c r="T192" s="1"/>
+      <c r="T192" s="24"/>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
@@ -15989,7 +16186,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
-      <c r="T193" s="1"/>
+      <c r="T193" s="24"/>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
@@ -16044,7 +16241,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
-      <c r="T194" s="1"/>
+      <c r="T194" s="24"/>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
@@ -16099,7 +16296,7 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
-      <c r="T195" s="1"/>
+      <c r="T195" s="24"/>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
@@ -16154,7 +16351,7 @@
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
-      <c r="T196" s="1"/>
+      <c r="T196" s="24"/>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
@@ -16209,7 +16406,7 @@
       <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
-      <c r="T197" s="1"/>
+      <c r="T197" s="24"/>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
@@ -16264,7 +16461,7 @@
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
-      <c r="T198" s="1"/>
+      <c r="T198" s="24"/>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
@@ -16319,7 +16516,7 @@
       <c r="Q199" s="1"/>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
-      <c r="T199" s="1"/>
+      <c r="T199" s="24"/>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
@@ -16374,7 +16571,7 @@
       <c r="Q200" s="1"/>
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
-      <c r="T200" s="1"/>
+      <c r="T200" s="24"/>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
@@ -16429,7 +16626,7 @@
       <c r="Q201" s="1"/>
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
-      <c r="T201" s="1"/>
+      <c r="T201" s="24"/>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
@@ -16484,7 +16681,7 @@
       <c r="Q202" s="1"/>
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
-      <c r="T202" s="1"/>
+      <c r="T202" s="24"/>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
@@ -16539,7 +16736,7 @@
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
-      <c r="T203" s="1"/>
+      <c r="T203" s="24"/>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
@@ -16594,7 +16791,7 @@
       <c r="Q204" s="1"/>
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
-      <c r="T204" s="1"/>
+      <c r="T204" s="24"/>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
@@ -16649,7 +16846,7 @@
       <c r="Q205" s="1"/>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
-      <c r="T205" s="1"/>
+      <c r="T205" s="24"/>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
@@ -16704,7 +16901,7 @@
       <c r="Q206" s="1"/>
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
-      <c r="T206" s="1"/>
+      <c r="T206" s="24"/>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
@@ -16759,7 +16956,7 @@
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
-      <c r="T207" s="1"/>
+      <c r="T207" s="24"/>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
@@ -16814,7 +17011,7 @@
       <c r="Q208" s="1"/>
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
-      <c r="T208" s="1"/>
+      <c r="T208" s="24"/>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
@@ -16869,7 +17066,7 @@
       <c r="Q209" s="1"/>
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
-      <c r="T209" s="1"/>
+      <c r="T209" s="24"/>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
@@ -16924,7 +17121,7 @@
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
-      <c r="T210" s="1"/>
+      <c r="T210" s="24"/>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
@@ -16979,7 +17176,7 @@
       <c r="Q211" s="1"/>
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
-      <c r="T211" s="1"/>
+      <c r="T211" s="24"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
@@ -17034,7 +17231,7 @@
       <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
-      <c r="T212" s="1"/>
+      <c r="T212" s="24"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
@@ -17089,7 +17286,7 @@
       <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
-      <c r="T213" s="1"/>
+      <c r="T213" s="24"/>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
@@ -17144,7 +17341,7 @@
       <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
-      <c r="T214" s="1"/>
+      <c r="T214" s="24"/>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
@@ -17199,7 +17396,7 @@
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
+      <c r="T215" s="24"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
@@ -17254,7 +17451,7 @@
       <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
-      <c r="T216" s="1"/>
+      <c r="T216" s="24"/>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
@@ -17309,7 +17506,7 @@
       <c r="Q217" s="1"/>
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
-      <c r="T217" s="1"/>
+      <c r="T217" s="24"/>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
@@ -17364,7 +17561,7 @@
       <c r="Q218" s="1"/>
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
-      <c r="T218" s="1"/>
+      <c r="T218" s="24"/>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
@@ -17419,7 +17616,7 @@
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
-      <c r="T219" s="1"/>
+      <c r="T219" s="24"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
@@ -17474,7 +17671,7 @@
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
-      <c r="T220" s="1"/>
+      <c r="T220" s="24"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
@@ -17529,7 +17726,7 @@
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
-      <c r="T221" s="1"/>
+      <c r="T221" s="24"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
@@ -17584,7 +17781,7 @@
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
-      <c r="T222" s="1"/>
+      <c r="T222" s="24"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
@@ -17639,7 +17836,7 @@
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
-      <c r="T223" s="1"/>
+      <c r="T223" s="24"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
@@ -17694,7 +17891,7 @@
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
-      <c r="T224" s="1"/>
+      <c r="T224" s="24"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
@@ -17749,7 +17946,7 @@
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
-      <c r="T225" s="1"/>
+      <c r="T225" s="24"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
@@ -17804,7 +18001,7 @@
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
-      <c r="T226" s="1"/>
+      <c r="T226" s="24"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
@@ -17859,7 +18056,7 @@
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
-      <c r="T227" s="1"/>
+      <c r="T227" s="24"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
@@ -17914,7 +18111,7 @@
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
-      <c r="T228" s="1"/>
+      <c r="T228" s="24"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
@@ -17969,7 +18166,7 @@
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
+      <c r="T229" s="24"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
@@ -18024,7 +18221,7 @@
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
-      <c r="T230" s="1"/>
+      <c r="T230" s="24"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
@@ -18079,7 +18276,7 @@
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
-      <c r="T231" s="1"/>
+      <c r="T231" s="24"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
@@ -18134,7 +18331,7 @@
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
-      <c r="T232" s="1"/>
+      <c r="T232" s="24"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
@@ -18189,7 +18386,7 @@
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
-      <c r="T233" s="1"/>
+      <c r="T233" s="24"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
@@ -18244,7 +18441,7 @@
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
-      <c r="T234" s="1"/>
+      <c r="T234" s="24"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
@@ -18299,7 +18496,7 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
-      <c r="T235" s="1"/>
+      <c r="T235" s="24"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
@@ -18354,7 +18551,7 @@
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
-      <c r="T236" s="1"/>
+      <c r="T236" s="24"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
@@ -18409,7 +18606,7 @@
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
-      <c r="T237" s="1"/>
+      <c r="T237" s="24"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
@@ -18464,7 +18661,7 @@
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
-      <c r="T238" s="1"/>
+      <c r="T238" s="24"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
@@ -18519,7 +18716,7 @@
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
-      <c r="T239" s="1"/>
+      <c r="T239" s="24"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
@@ -18574,7 +18771,7 @@
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
-      <c r="T240" s="1"/>
+      <c r="T240" s="24"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
@@ -18629,7 +18826,7 @@
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
-      <c r="T241" s="1"/>
+      <c r="T241" s="24"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
@@ -18684,7 +18881,7 @@
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
-      <c r="T242" s="1"/>
+      <c r="T242" s="24"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
@@ -18739,7 +18936,7 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
-      <c r="T243" s="1"/>
+      <c r="T243" s="24"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
@@ -18794,7 +18991,7 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
-      <c r="T244" s="1"/>
+      <c r="T244" s="24"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
@@ -18849,7 +19046,7 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
-      <c r="T245" s="1"/>
+      <c r="T245" s="24"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
@@ -18904,7 +19101,7 @@
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
-      <c r="T246" s="1"/>
+      <c r="T246" s="24"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
@@ -18959,7 +19156,7 @@
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
-      <c r="T247" s="1"/>
+      <c r="T247" s="24"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
@@ -19014,7 +19211,7 @@
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
-      <c r="T248" s="1"/>
+      <c r="T248" s="24"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
@@ -19069,7 +19266,7 @@
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
-      <c r="T249" s="1"/>
+      <c r="T249" s="24"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
@@ -19124,7 +19321,7 @@
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
-      <c r="T250" s="1"/>
+      <c r="T250" s="24"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
@@ -19179,7 +19376,7 @@
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
-      <c r="T251" s="1"/>
+      <c r="T251" s="24"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
@@ -19234,7 +19431,7 @@
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
-      <c r="T252" s="1"/>
+      <c r="T252" s="24"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
@@ -19289,7 +19486,7 @@
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
-      <c r="T253" s="1"/>
+      <c r="T253" s="24"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
@@ -19344,7 +19541,7 @@
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
-      <c r="T254" s="1"/>
+      <c r="T254" s="24"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
@@ -19399,7 +19596,7 @@
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
-      <c r="T255" s="1"/>
+      <c r="T255" s="24"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
@@ -19454,7 +19651,7 @@
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
-      <c r="T256" s="1"/>
+      <c r="T256" s="24"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
@@ -19509,7 +19706,7 @@
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
-      <c r="T257" s="1"/>
+      <c r="T257" s="24"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
@@ -19564,7 +19761,7 @@
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
-      <c r="T258" s="1"/>
+      <c r="T258" s="24"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
@@ -19619,7 +19816,7 @@
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
-      <c r="T259" s="1"/>
+      <c r="T259" s="24"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
@@ -19674,7 +19871,7 @@
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
-      <c r="T260" s="1"/>
+      <c r="T260" s="24"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
@@ -19729,7 +19926,7 @@
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
-      <c r="T261" s="1"/>
+      <c r="T261" s="24"/>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
@@ -19784,7 +19981,7 @@
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
-      <c r="T262" s="1"/>
+      <c r="T262" s="24"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
@@ -19839,7 +20036,7 @@
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
-      <c r="T263" s="1"/>
+      <c r="T263" s="24"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
@@ -19894,7 +20091,7 @@
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
-      <c r="T264" s="1"/>
+      <c r="T264" s="24"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
@@ -19949,7 +20146,7 @@
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
-      <c r="T265" s="1"/>
+      <c r="T265" s="24"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
@@ -20004,7 +20201,7 @@
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
-      <c r="T266" s="1"/>
+      <c r="T266" s="24"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
@@ -20059,7 +20256,7 @@
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
-      <c r="T267" s="1"/>
+      <c r="T267" s="24"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
@@ -20114,7 +20311,7 @@
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
-      <c r="T268" s="1"/>
+      <c r="T268" s="24"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
@@ -20169,7 +20366,7 @@
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
-      <c r="T269" s="1"/>
+      <c r="T269" s="24"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
@@ -20224,7 +20421,7 @@
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
-      <c r="T270" s="1"/>
+      <c r="T270" s="24"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
@@ -20279,7 +20476,7 @@
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
-      <c r="T271" s="1"/>
+      <c r="T271" s="24"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
@@ -20334,7 +20531,7 @@
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
-      <c r="T272" s="1"/>
+      <c r="T272" s="24"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
@@ -20389,7 +20586,7 @@
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
-      <c r="T273" s="1"/>
+      <c r="T273" s="24"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
@@ -20444,7 +20641,7 @@
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
-      <c r="T274" s="1"/>
+      <c r="T274" s="24"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
@@ -20499,7 +20696,7 @@
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
+      <c r="T275" s="24"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
@@ -20554,7 +20751,7 @@
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
+      <c r="T276" s="24"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
@@ -20609,7 +20806,7 @@
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
+      <c r="T277" s="24"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
@@ -20664,7 +20861,7 @@
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
+      <c r="T278" s="24"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
@@ -20719,7 +20916,7 @@
       <c r="Q279" s="1"/>
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
+      <c r="T279" s="24"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
@@ -20774,7 +20971,7 @@
       <c r="Q280" s="1"/>
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
+      <c r="T280" s="24"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
@@ -20829,7 +21026,7 @@
       <c r="Q281" s="1"/>
       <c r="R281" s="1"/>
       <c r="S281" s="1"/>
-      <c r="T281" s="1"/>
+      <c r="T281" s="24"/>
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
       <c r="W281" s="1"/>
@@ -20884,7 +21081,7 @@
       <c r="Q282" s="1"/>
       <c r="R282" s="1"/>
       <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
+      <c r="T282" s="24"/>
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
       <c r="W282" s="1"/>
@@ -20939,7 +21136,7 @@
       <c r="Q283" s="1"/>
       <c r="R283" s="1"/>
       <c r="S283" s="1"/>
-      <c r="T283" s="1"/>
+      <c r="T283" s="24"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
@@ -20994,7 +21191,7 @@
       <c r="Q284" s="1"/>
       <c r="R284" s="1"/>
       <c r="S284" s="1"/>
-      <c r="T284" s="1"/>
+      <c r="T284" s="24"/>
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
       <c r="W284" s="1"/>
@@ -21049,7 +21246,7 @@
       <c r="Q285" s="1"/>
       <c r="R285" s="1"/>
       <c r="S285" s="1"/>
-      <c r="T285" s="1"/>
+      <c r="T285" s="24"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
@@ -21104,7 +21301,7 @@
       <c r="Q286" s="1"/>
       <c r="R286" s="1"/>
       <c r="S286" s="1"/>
-      <c r="T286" s="1"/>
+      <c r="T286" s="24"/>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
@@ -21159,7 +21356,7 @@
       <c r="Q287" s="1"/>
       <c r="R287" s="1"/>
       <c r="S287" s="1"/>
-      <c r="T287" s="1"/>
+      <c r="T287" s="24"/>
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
@@ -21214,7 +21411,7 @@
       <c r="Q288" s="1"/>
       <c r="R288" s="1"/>
       <c r="S288" s="1"/>
-      <c r="T288" s="1"/>
+      <c r="T288" s="24"/>
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
       <c r="W288" s="1"/>
@@ -21269,7 +21466,7 @@
       <c r="Q289" s="1"/>
       <c r="R289" s="1"/>
       <c r="S289" s="1"/>
-      <c r="T289" s="1"/>
+      <c r="T289" s="24"/>
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
       <c r="W289" s="1"/>
@@ -21324,7 +21521,7 @@
       <c r="Q290" s="1"/>
       <c r="R290" s="1"/>
       <c r="S290" s="1"/>
-      <c r="T290" s="1"/>
+      <c r="T290" s="24"/>
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
       <c r="W290" s="1"/>
@@ -21379,7 +21576,7 @@
       <c r="Q291" s="1"/>
       <c r="R291" s="1"/>
       <c r="S291" s="1"/>
-      <c r="T291" s="1"/>
+      <c r="T291" s="24"/>
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
       <c r="W291" s="1"/>
@@ -21434,7 +21631,7 @@
       <c r="Q292" s="1"/>
       <c r="R292" s="1"/>
       <c r="S292" s="1"/>
-      <c r="T292" s="1"/>
+      <c r="T292" s="24"/>
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
       <c r="W292" s="1"/>
@@ -21489,7 +21686,7 @@
       <c r="Q293" s="1"/>
       <c r="R293" s="1"/>
       <c r="S293" s="1"/>
-      <c r="T293" s="1"/>
+      <c r="T293" s="24"/>
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
       <c r="W293" s="1"/>
@@ -21544,7 +21741,7 @@
       <c r="Q294" s="1"/>
       <c r="R294" s="1"/>
       <c r="S294" s="1"/>
-      <c r="T294" s="1"/>
+      <c r="T294" s="24"/>
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
       <c r="W294" s="1"/>
@@ -21599,7 +21796,7 @@
       <c r="Q295" s="1"/>
       <c r="R295" s="1"/>
       <c r="S295" s="1"/>
-      <c r="T295" s="1"/>
+      <c r="T295" s="24"/>
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
       <c r="W295" s="1"/>
@@ -21654,7 +21851,7 @@
       <c r="Q296" s="1"/>
       <c r="R296" s="1"/>
       <c r="S296" s="1"/>
-      <c r="T296" s="1"/>
+      <c r="T296" s="24"/>
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
       <c r="W296" s="1"/>
@@ -21709,7 +21906,7 @@
       <c r="Q297" s="1"/>
       <c r="R297" s="1"/>
       <c r="S297" s="1"/>
-      <c r="T297" s="1"/>
+      <c r="T297" s="24"/>
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
       <c r="W297" s="1"/>
@@ -21764,7 +21961,7 @@
       <c r="Q298" s="1"/>
       <c r="R298" s="1"/>
       <c r="S298" s="1"/>
-      <c r="T298" s="1"/>
+      <c r="T298" s="24"/>
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
       <c r="W298" s="1"/>
@@ -21819,7 +22016,7 @@
       <c r="Q299" s="1"/>
       <c r="R299" s="1"/>
       <c r="S299" s="1"/>
-      <c r="T299" s="1"/>
+      <c r="T299" s="24"/>
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
       <c r="W299" s="1"/>
@@ -21874,7 +22071,7 @@
       <c r="Q300" s="1"/>
       <c r="R300" s="1"/>
       <c r="S300" s="1"/>
-      <c r="T300" s="1"/>
+      <c r="T300" s="24"/>
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
       <c r="W300" s="1"/>
@@ -21929,7 +22126,7 @@
       <c r="Q301" s="1"/>
       <c r="R301" s="1"/>
       <c r="S301" s="1"/>
-      <c r="T301" s="1"/>
+      <c r="T301" s="24"/>
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
       <c r="W301" s="1"/>
@@ -21984,7 +22181,7 @@
       <c r="Q302" s="1"/>
       <c r="R302" s="1"/>
       <c r="S302" s="1"/>
-      <c r="T302" s="1"/>
+      <c r="T302" s="24"/>
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
       <c r="W302" s="1"/>
@@ -22039,7 +22236,7 @@
       <c r="Q303" s="1"/>
       <c r="R303" s="1"/>
       <c r="S303" s="1"/>
-      <c r="T303" s="1"/>
+      <c r="T303" s="24"/>
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
       <c r="W303" s="1"/>
@@ -22094,7 +22291,7 @@
       <c r="Q304" s="1"/>
       <c r="R304" s="1"/>
       <c r="S304" s="1"/>
-      <c r="T304" s="1"/>
+      <c r="T304" s="24"/>
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
       <c r="W304" s="1"/>
@@ -22149,7 +22346,7 @@
       <c r="Q305" s="1"/>
       <c r="R305" s="1"/>
       <c r="S305" s="1"/>
-      <c r="T305" s="1"/>
+      <c r="T305" s="24"/>
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
       <c r="W305" s="1"/>
@@ -22204,7 +22401,7 @@
       <c r="Q306" s="1"/>
       <c r="R306" s="1"/>
       <c r="S306" s="1"/>
-      <c r="T306" s="1"/>
+      <c r="T306" s="24"/>
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
       <c r="W306" s="1"/>
@@ -22259,7 +22456,7 @@
       <c r="Q307" s="1"/>
       <c r="R307" s="1"/>
       <c r="S307" s="1"/>
-      <c r="T307" s="1"/>
+      <c r="T307" s="24"/>
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
       <c r="W307" s="1"/>
@@ -22314,7 +22511,7 @@
       <c r="Q308" s="1"/>
       <c r="R308" s="1"/>
       <c r="S308" s="1"/>
-      <c r="T308" s="1"/>
+      <c r="T308" s="24"/>
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
       <c r="W308" s="1"/>
@@ -22369,7 +22566,7 @@
       <c r="Q309" s="1"/>
       <c r="R309" s="1"/>
       <c r="S309" s="1"/>
-      <c r="T309" s="1"/>
+      <c r="T309" s="24"/>
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
@@ -22424,7 +22621,7 @@
       <c r="Q310" s="1"/>
       <c r="R310" s="1"/>
       <c r="S310" s="1"/>
-      <c r="T310" s="1"/>
+      <c r="T310" s="24"/>
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
@@ -22479,7 +22676,7 @@
       <c r="Q311" s="1"/>
       <c r="R311" s="1"/>
       <c r="S311" s="1"/>
-      <c r="T311" s="1"/>
+      <c r="T311" s="24"/>
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
       <c r="W311" s="1"/>
@@ -22534,7 +22731,7 @@
       <c r="Q312" s="1"/>
       <c r="R312" s="1"/>
       <c r="S312" s="1"/>
-      <c r="T312" s="1"/>
+      <c r="T312" s="24"/>
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
       <c r="W312" s="1"/>
@@ -22589,7 +22786,7 @@
       <c r="Q313" s="1"/>
       <c r="R313" s="1"/>
       <c r="S313" s="1"/>
-      <c r="T313" s="1"/>
+      <c r="T313" s="24"/>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
       <c r="W313" s="1"/>
@@ -22644,7 +22841,7 @@
       <c r="Q314" s="1"/>
       <c r="R314" s="1"/>
       <c r="S314" s="1"/>
-      <c r="T314" s="1"/>
+      <c r="T314" s="24"/>
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
       <c r="W314" s="1"/>
@@ -22699,7 +22896,7 @@
       <c r="Q315" s="1"/>
       <c r="R315" s="1"/>
       <c r="S315" s="1"/>
-      <c r="T315" s="1"/>
+      <c r="T315" s="24"/>
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
       <c r="W315" s="1"/>
@@ -22754,7 +22951,7 @@
       <c r="Q316" s="1"/>
       <c r="R316" s="1"/>
       <c r="S316" s="1"/>
-      <c r="T316" s="1"/>
+      <c r="T316" s="24"/>
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
       <c r="W316" s="1"/>
@@ -22809,7 +23006,7 @@
       <c r="Q317" s="1"/>
       <c r="R317" s="1"/>
       <c r="S317" s="1"/>
-      <c r="T317" s="1"/>
+      <c r="T317" s="24"/>
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
       <c r="W317" s="1"/>
@@ -22864,7 +23061,7 @@
       <c r="Q318" s="1"/>
       <c r="R318" s="1"/>
       <c r="S318" s="1"/>
-      <c r="T318" s="1"/>
+      <c r="T318" s="24"/>
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
       <c r="W318" s="1"/>
@@ -22919,7 +23116,7 @@
       <c r="Q319" s="1"/>
       <c r="R319" s="1"/>
       <c r="S319" s="1"/>
-      <c r="T319" s="1"/>
+      <c r="T319" s="24"/>
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
       <c r="W319" s="1"/>
@@ -22974,7 +23171,7 @@
       <c r="Q320" s="1"/>
       <c r="R320" s="1"/>
       <c r="S320" s="1"/>
-      <c r="T320" s="1"/>
+      <c r="T320" s="24"/>
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
       <c r="W320" s="1"/>
@@ -23029,7 +23226,7 @@
       <c r="Q321" s="1"/>
       <c r="R321" s="1"/>
       <c r="S321" s="1"/>
-      <c r="T321" s="1"/>
+      <c r="T321" s="24"/>
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
       <c r="W321" s="1"/>
@@ -23084,7 +23281,7 @@
       <c r="Q322" s="1"/>
       <c r="R322" s="1"/>
       <c r="S322" s="1"/>
-      <c r="T322" s="1"/>
+      <c r="T322" s="24"/>
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
       <c r="W322" s="1"/>
@@ -23139,7 +23336,7 @@
       <c r="Q323" s="1"/>
       <c r="R323" s="1"/>
       <c r="S323" s="1"/>
-      <c r="T323" s="1"/>
+      <c r="T323" s="24"/>
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
       <c r="W323" s="1"/>
@@ -23194,7 +23391,7 @@
       <c r="Q324" s="1"/>
       <c r="R324" s="1"/>
       <c r="S324" s="1"/>
-      <c r="T324" s="1"/>
+      <c r="T324" s="24"/>
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
       <c r="W324" s="1"/>
@@ -23249,7 +23446,7 @@
       <c r="Q325" s="1"/>
       <c r="R325" s="1"/>
       <c r="S325" s="1"/>
-      <c r="T325" s="1"/>
+      <c r="T325" s="24"/>
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
       <c r="W325" s="1"/>
@@ -23304,7 +23501,7 @@
       <c r="Q326" s="1"/>
       <c r="R326" s="1"/>
       <c r="S326" s="1"/>
-      <c r="T326" s="1"/>
+      <c r="T326" s="24"/>
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
       <c r="W326" s="1"/>
@@ -23359,7 +23556,7 @@
       <c r="Q327" s="1"/>
       <c r="R327" s="1"/>
       <c r="S327" s="1"/>
-      <c r="T327" s="1"/>
+      <c r="T327" s="24"/>
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
       <c r="W327" s="1"/>
@@ -23414,7 +23611,7 @@
       <c r="Q328" s="1"/>
       <c r="R328" s="1"/>
       <c r="S328" s="1"/>
-      <c r="T328" s="1"/>
+      <c r="T328" s="24"/>
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
       <c r="W328" s="1"/>
@@ -23469,7 +23666,7 @@
       <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
-      <c r="T329" s="1"/>
+      <c r="T329" s="24"/>
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
       <c r="W329" s="1"/>
@@ -23524,7 +23721,7 @@
       <c r="Q330" s="1"/>
       <c r="R330" s="1"/>
       <c r="S330" s="1"/>
-      <c r="T330" s="1"/>
+      <c r="T330" s="24"/>
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
       <c r="W330" s="1"/>
@@ -23579,7 +23776,7 @@
       <c r="Q331" s="1"/>
       <c r="R331" s="1"/>
       <c r="S331" s="1"/>
-      <c r="T331" s="1"/>
+      <c r="T331" s="24"/>
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
       <c r="W331" s="1"/>
@@ -23634,7 +23831,7 @@
       <c r="Q332" s="1"/>
       <c r="R332" s="1"/>
       <c r="S332" s="1"/>
-      <c r="T332" s="1"/>
+      <c r="T332" s="24"/>
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
       <c r="W332" s="1"/>
@@ -23689,7 +23886,7 @@
       <c r="Q333" s="1"/>
       <c r="R333" s="1"/>
       <c r="S333" s="1"/>
-      <c r="T333" s="1"/>
+      <c r="T333" s="24"/>
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
       <c r="W333" s="1"/>
@@ -23744,7 +23941,7 @@
       <c r="Q334" s="1"/>
       <c r="R334" s="1"/>
       <c r="S334" s="1"/>
-      <c r="T334" s="1"/>
+      <c r="T334" s="24"/>
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
@@ -23799,7 +23996,7 @@
       <c r="Q335" s="1"/>
       <c r="R335" s="1"/>
       <c r="S335" s="1"/>
-      <c r="T335" s="1"/>
+      <c r="T335" s="24"/>
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
       <c r="W335" s="1"/>
@@ -23854,7 +24051,7 @@
       <c r="Q336" s="1"/>
       <c r="R336" s="1"/>
       <c r="S336" s="1"/>
-      <c r="T336" s="1"/>
+      <c r="T336" s="24"/>
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
       <c r="W336" s="1"/>
@@ -23909,7 +24106,7 @@
       <c r="Q337" s="1"/>
       <c r="R337" s="1"/>
       <c r="S337" s="1"/>
-      <c r="T337" s="1"/>
+      <c r="T337" s="24"/>
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
       <c r="W337" s="1"/>
@@ -23964,7 +24161,7 @@
       <c r="Q338" s="1"/>
       <c r="R338" s="1"/>
       <c r="S338" s="1"/>
-      <c r="T338" s="1"/>
+      <c r="T338" s="24"/>
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
       <c r="W338" s="1"/>
@@ -24019,7 +24216,7 @@
       <c r="Q339" s="1"/>
       <c r="R339" s="1"/>
       <c r="S339" s="1"/>
-      <c r="T339" s="1"/>
+      <c r="T339" s="24"/>
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
       <c r="W339" s="1"/>
@@ -24074,7 +24271,7 @@
       <c r="Q340" s="1"/>
       <c r="R340" s="1"/>
       <c r="S340" s="1"/>
-      <c r="T340" s="1"/>
+      <c r="T340" s="24"/>
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
       <c r="W340" s="1"/>
@@ -24129,7 +24326,7 @@
       <c r="Q341" s="1"/>
       <c r="R341" s="1"/>
       <c r="S341" s="1"/>
-      <c r="T341" s="1"/>
+      <c r="T341" s="24"/>
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
@@ -24184,7 +24381,7 @@
       <c r="Q342" s="1"/>
       <c r="R342" s="1"/>
       <c r="S342" s="1"/>
-      <c r="T342" s="1"/>
+      <c r="T342" s="24"/>
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
       <c r="W342" s="1"/>
@@ -24239,7 +24436,7 @@
       <c r="Q343" s="1"/>
       <c r="R343" s="1"/>
       <c r="S343" s="1"/>
-      <c r="T343" s="1"/>
+      <c r="T343" s="24"/>
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
       <c r="W343" s="1"/>
@@ -24294,7 +24491,7 @@
       <c r="Q344" s="1"/>
       <c r="R344" s="1"/>
       <c r="S344" s="1"/>
-      <c r="T344" s="1"/>
+      <c r="T344" s="24"/>
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
@@ -24349,7 +24546,7 @@
       <c r="Q345" s="1"/>
       <c r="R345" s="1"/>
       <c r="S345" s="1"/>
-      <c r="T345" s="1"/>
+      <c r="T345" s="24"/>
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
       <c r="W345" s="1"/>
@@ -24404,7 +24601,7 @@
       <c r="Q346" s="1"/>
       <c r="R346" s="1"/>
       <c r="S346" s="1"/>
-      <c r="T346" s="1"/>
+      <c r="T346" s="24"/>
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
       <c r="W346" s="1"/>
@@ -24459,7 +24656,7 @@
       <c r="Q347" s="1"/>
       <c r="R347" s="1"/>
       <c r="S347" s="1"/>
-      <c r="T347" s="1"/>
+      <c r="T347" s="24"/>
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
       <c r="W347" s="1"/>
@@ -24514,7 +24711,7 @@
       <c r="Q348" s="1"/>
       <c r="R348" s="1"/>
       <c r="S348" s="1"/>
-      <c r="T348" s="1"/>
+      <c r="T348" s="24"/>
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
       <c r="W348" s="1"/>
@@ -24569,7 +24766,7 @@
       <c r="Q349" s="1"/>
       <c r="R349" s="1"/>
       <c r="S349" s="1"/>
-      <c r="T349" s="1"/>
+      <c r="T349" s="24"/>
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
       <c r="W349" s="1"/>
@@ -24624,7 +24821,7 @@
       <c r="Q350" s="1"/>
       <c r="R350" s="1"/>
       <c r="S350" s="1"/>
-      <c r="T350" s="1"/>
+      <c r="T350" s="24"/>
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
       <c r="W350" s="1"/>
@@ -24679,7 +24876,7 @@
       <c r="Q351" s="1"/>
       <c r="R351" s="1"/>
       <c r="S351" s="1"/>
-      <c r="T351" s="1"/>
+      <c r="T351" s="24"/>
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
       <c r="W351" s="1"/>
@@ -24734,7 +24931,7 @@
       <c r="Q352" s="1"/>
       <c r="R352" s="1"/>
       <c r="S352" s="1"/>
-      <c r="T352" s="1"/>
+      <c r="T352" s="24"/>
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
       <c r="W352" s="1"/>
@@ -24789,7 +24986,7 @@
       <c r="Q353" s="1"/>
       <c r="R353" s="1"/>
       <c r="S353" s="1"/>
-      <c r="T353" s="1"/>
+      <c r="T353" s="24"/>
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
       <c r="W353" s="1"/>
@@ -24844,7 +25041,7 @@
       <c r="Q354" s="1"/>
       <c r="R354" s="1"/>
       <c r="S354" s="1"/>
-      <c r="T354" s="1"/>
+      <c r="T354" s="24"/>
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
       <c r="W354" s="1"/>
@@ -24899,7 +25096,7 @@
       <c r="Q355" s="1"/>
       <c r="R355" s="1"/>
       <c r="S355" s="1"/>
-      <c r="T355" s="1"/>
+      <c r="T355" s="24"/>
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
       <c r="W355" s="1"/>
@@ -24954,7 +25151,7 @@
       <c r="Q356" s="1"/>
       <c r="R356" s="1"/>
       <c r="S356" s="1"/>
-      <c r="T356" s="1"/>
+      <c r="T356" s="24"/>
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
       <c r="W356" s="1"/>
@@ -25009,7 +25206,7 @@
       <c r="Q357" s="1"/>
       <c r="R357" s="1"/>
       <c r="S357" s="1"/>
-      <c r="T357" s="1"/>
+      <c r="T357" s="24"/>
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
       <c r="W357" s="1"/>
@@ -25064,7 +25261,7 @@
       <c r="Q358" s="1"/>
       <c r="R358" s="1"/>
       <c r="S358" s="1"/>
-      <c r="T358" s="1"/>
+      <c r="T358" s="24"/>
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
       <c r="W358" s="1"/>
@@ -25119,7 +25316,7 @@
       <c r="Q359" s="1"/>
       <c r="R359" s="1"/>
       <c r="S359" s="1"/>
-      <c r="T359" s="1"/>
+      <c r="T359" s="24"/>
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
       <c r="W359" s="1"/>
@@ -25174,7 +25371,7 @@
       <c r="Q360" s="1"/>
       <c r="R360" s="1"/>
       <c r="S360" s="1"/>
-      <c r="T360" s="1"/>
+      <c r="T360" s="24"/>
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
       <c r="W360" s="1"/>
@@ -25229,7 +25426,7 @@
       <c r="Q361" s="1"/>
       <c r="R361" s="1"/>
       <c r="S361" s="1"/>
-      <c r="T361" s="1"/>
+      <c r="T361" s="24"/>
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
       <c r="W361" s="1"/>
@@ -25284,7 +25481,7 @@
       <c r="Q362" s="1"/>
       <c r="R362" s="1"/>
       <c r="S362" s="1"/>
-      <c r="T362" s="1"/>
+      <c r="T362" s="24"/>
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
       <c r="W362" s="1"/>
@@ -25339,7 +25536,7 @@
       <c r="Q363" s="1"/>
       <c r="R363" s="1"/>
       <c r="S363" s="1"/>
-      <c r="T363" s="1"/>
+      <c r="T363" s="24"/>
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
       <c r="W363" s="1"/>
@@ -25394,7 +25591,7 @@
       <c r="Q364" s="1"/>
       <c r="R364" s="1"/>
       <c r="S364" s="1"/>
-      <c r="T364" s="1"/>
+      <c r="T364" s="24"/>
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
       <c r="W364" s="1"/>
@@ -25449,7 +25646,7 @@
       <c r="Q365" s="1"/>
       <c r="R365" s="1"/>
       <c r="S365" s="1"/>
-      <c r="T365" s="1"/>
+      <c r="T365" s="24"/>
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
       <c r="W365" s="1"/>
@@ -25504,7 +25701,7 @@
       <c r="Q366" s="1"/>
       <c r="R366" s="1"/>
       <c r="S366" s="1"/>
-      <c r="T366" s="1"/>
+      <c r="T366" s="24"/>
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
       <c r="W366" s="1"/>
@@ -25559,7 +25756,7 @@
       <c r="Q367" s="1"/>
       <c r="R367" s="1"/>
       <c r="S367" s="1"/>
-      <c r="T367" s="1"/>
+      <c r="T367" s="24"/>
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
       <c r="W367" s="1"/>
@@ -25614,7 +25811,7 @@
       <c r="Q368" s="1"/>
       <c r="R368" s="1"/>
       <c r="S368" s="1"/>
-      <c r="T368" s="1"/>
+      <c r="T368" s="24"/>
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
       <c r="W368" s="1"/>
@@ -25669,7 +25866,7 @@
       <c r="Q369" s="1"/>
       <c r="R369" s="1"/>
       <c r="S369" s="1"/>
-      <c r="T369" s="1"/>
+      <c r="T369" s="24"/>
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
       <c r="W369" s="1"/>
@@ -25724,7 +25921,7 @@
       <c r="Q370" s="1"/>
       <c r="R370" s="1"/>
       <c r="S370" s="1"/>
-      <c r="T370" s="1"/>
+      <c r="T370" s="24"/>
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
       <c r="W370" s="1"/>
@@ -25779,7 +25976,7 @@
       <c r="Q371" s="1"/>
       <c r="R371" s="1"/>
       <c r="S371" s="1"/>
-      <c r="T371" s="1"/>
+      <c r="T371" s="24"/>
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
       <c r="W371" s="1"/>
@@ -25834,7 +26031,7 @@
       <c r="Q372" s="1"/>
       <c r="R372" s="1"/>
       <c r="S372" s="1"/>
-      <c r="T372" s="1"/>
+      <c r="T372" s="24"/>
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
       <c r="W372" s="1"/>
@@ -25889,7 +26086,7 @@
       <c r="Q373" s="1"/>
       <c r="R373" s="1"/>
       <c r="S373" s="1"/>
-      <c r="T373" s="1"/>
+      <c r="T373" s="24"/>
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
       <c r="W373" s="1"/>
@@ -25944,7 +26141,7 @@
       <c r="Q374" s="1"/>
       <c r="R374" s="1"/>
       <c r="S374" s="1"/>
-      <c r="T374" s="1"/>
+      <c r="T374" s="24"/>
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
       <c r="W374" s="1"/>
@@ -25999,7 +26196,7 @@
       <c r="Q375" s="1"/>
       <c r="R375" s="1"/>
       <c r="S375" s="1"/>
-      <c r="T375" s="1"/>
+      <c r="T375" s="24"/>
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
       <c r="W375" s="1"/>
@@ -26054,7 +26251,7 @@
       <c r="Q376" s="1"/>
       <c r="R376" s="1"/>
       <c r="S376" s="1"/>
-      <c r="T376" s="1"/>
+      <c r="T376" s="24"/>
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
       <c r="W376" s="1"/>
@@ -26109,7 +26306,7 @@
       <c r="Q377" s="1"/>
       <c r="R377" s="1"/>
       <c r="S377" s="1"/>
-      <c r="T377" s="1"/>
+      <c r="T377" s="24"/>
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
       <c r="W377" s="1"/>
@@ -26164,7 +26361,7 @@
       <c r="Q378" s="1"/>
       <c r="R378" s="1"/>
       <c r="S378" s="1"/>
-      <c r="T378" s="1"/>
+      <c r="T378" s="24"/>
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
       <c r="W378" s="1"/>
@@ -26219,7 +26416,7 @@
       <c r="Q379" s="1"/>
       <c r="R379" s="1"/>
       <c r="S379" s="1"/>
-      <c r="T379" s="1"/>
+      <c r="T379" s="24"/>
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
       <c r="W379" s="1"/>
@@ -26274,7 +26471,7 @@
       <c r="Q380" s="1"/>
       <c r="R380" s="1"/>
       <c r="S380" s="1"/>
-      <c r="T380" s="1"/>
+      <c r="T380" s="24"/>
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
       <c r="W380" s="1"/>
@@ -26329,7 +26526,7 @@
       <c r="Q381" s="1"/>
       <c r="R381" s="1"/>
       <c r="S381" s="1"/>
-      <c r="T381" s="1"/>
+      <c r="T381" s="24"/>
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
       <c r="W381" s="1"/>
@@ -26384,7 +26581,7 @@
       <c r="Q382" s="1"/>
       <c r="R382" s="1"/>
       <c r="S382" s="1"/>
-      <c r="T382" s="1"/>
+      <c r="T382" s="24"/>
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
       <c r="W382" s="1"/>
@@ -26439,7 +26636,7 @@
       <c r="Q383" s="1"/>
       <c r="R383" s="1"/>
       <c r="S383" s="1"/>
-      <c r="T383" s="1"/>
+      <c r="T383" s="24"/>
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
       <c r="W383" s="1"/>
@@ -26494,7 +26691,7 @@
       <c r="Q384" s="1"/>
       <c r="R384" s="1"/>
       <c r="S384" s="1"/>
-      <c r="T384" s="1"/>
+      <c r="T384" s="24"/>
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
       <c r="W384" s="1"/>
@@ -26549,7 +26746,7 @@
       <c r="Q385" s="1"/>
       <c r="R385" s="1"/>
       <c r="S385" s="1"/>
-      <c r="T385" s="1"/>
+      <c r="T385" s="24"/>
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
       <c r="W385" s="1"/>
@@ -26604,7 +26801,7 @@
       <c r="Q386" s="1"/>
       <c r="R386" s="1"/>
       <c r="S386" s="1"/>
-      <c r="T386" s="1"/>
+      <c r="T386" s="24"/>
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
       <c r="W386" s="1"/>
@@ -26659,7 +26856,7 @@
       <c r="Q387" s="1"/>
       <c r="R387" s="1"/>
       <c r="S387" s="1"/>
-      <c r="T387" s="1"/>
+      <c r="T387" s="24"/>
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
       <c r="W387" s="1"/>
@@ -26714,7 +26911,7 @@
       <c r="Q388" s="1"/>
       <c r="R388" s="1"/>
       <c r="S388" s="1"/>
-      <c r="T388" s="1"/>
+      <c r="T388" s="24"/>
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
       <c r="W388" s="1"/>
@@ -26769,7 +26966,7 @@
       <c r="Q389" s="1"/>
       <c r="R389" s="1"/>
       <c r="S389" s="1"/>
-      <c r="T389" s="1"/>
+      <c r="T389" s="24"/>
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
       <c r="W389" s="1"/>
@@ -26824,7 +27021,7 @@
       <c r="Q390" s="1"/>
       <c r="R390" s="1"/>
       <c r="S390" s="1"/>
-      <c r="T390" s="1"/>
+      <c r="T390" s="24"/>
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
       <c r="W390" s="1"/>
@@ -26879,7 +27076,7 @@
       <c r="Q391" s="1"/>
       <c r="R391" s="1"/>
       <c r="S391" s="1"/>
-      <c r="T391" s="1"/>
+      <c r="T391" s="24"/>
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
       <c r="W391" s="1"/>
@@ -26934,7 +27131,7 @@
       <c r="Q392" s="1"/>
       <c r="R392" s="1"/>
       <c r="S392" s="1"/>
-      <c r="T392" s="1"/>
+      <c r="T392" s="24"/>
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
       <c r="W392" s="1"/>
@@ -26989,7 +27186,7 @@
       <c r="Q393" s="1"/>
       <c r="R393" s="1"/>
       <c r="S393" s="1"/>
-      <c r="T393" s="1"/>
+      <c r="T393" s="24"/>
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
       <c r="W393" s="1"/>
@@ -27044,7 +27241,7 @@
       <c r="Q394" s="1"/>
       <c r="R394" s="1"/>
       <c r="S394" s="1"/>
-      <c r="T394" s="1"/>
+      <c r="T394" s="24"/>
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
       <c r="W394" s="1"/>
@@ -27099,7 +27296,7 @@
       <c r="Q395" s="1"/>
       <c r="R395" s="1"/>
       <c r="S395" s="1"/>
-      <c r="T395" s="1"/>
+      <c r="T395" s="24"/>
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
       <c r="W395" s="1"/>
@@ -27154,7 +27351,7 @@
       <c r="Q396" s="1"/>
       <c r="R396" s="1"/>
       <c r="S396" s="1"/>
-      <c r="T396" s="1"/>
+      <c r="T396" s="24"/>
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
       <c r="W396" s="1"/>
@@ -27209,7 +27406,7 @@
       <c r="Q397" s="1"/>
       <c r="R397" s="1"/>
       <c r="S397" s="1"/>
-      <c r="T397" s="1"/>
+      <c r="T397" s="24"/>
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
       <c r="W397" s="1"/>
@@ -27264,7 +27461,7 @@
       <c r="Q398" s="1"/>
       <c r="R398" s="1"/>
       <c r="S398" s="1"/>
-      <c r="T398" s="1"/>
+      <c r="T398" s="24"/>
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
       <c r="W398" s="1"/>
@@ -27319,7 +27516,7 @@
       <c r="Q399" s="1"/>
       <c r="R399" s="1"/>
       <c r="S399" s="1"/>
-      <c r="T399" s="1"/>
+      <c r="T399" s="24"/>
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
       <c r="W399" s="1"/>
@@ -27374,7 +27571,7 @@
       <c r="Q400" s="1"/>
       <c r="R400" s="1"/>
       <c r="S400" s="1"/>
-      <c r="T400" s="1"/>
+      <c r="T400" s="24"/>
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
       <c r="W400" s="1"/>
@@ -27429,7 +27626,7 @@
       <c r="Q401" s="1"/>
       <c r="R401" s="1"/>
       <c r="S401" s="1"/>
-      <c r="T401" s="1"/>
+      <c r="T401" s="24"/>
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
       <c r="W401" s="1"/>
@@ -27484,7 +27681,7 @@
       <c r="Q402" s="1"/>
       <c r="R402" s="1"/>
       <c r="S402" s="1"/>
-      <c r="T402" s="1"/>
+      <c r="T402" s="24"/>
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
       <c r="W402" s="1"/>
@@ -27539,7 +27736,7 @@
       <c r="Q403" s="1"/>
       <c r="R403" s="1"/>
       <c r="S403" s="1"/>
-      <c r="T403" s="1"/>
+      <c r="T403" s="24"/>
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
       <c r="W403" s="1"/>
@@ -27594,7 +27791,7 @@
       <c r="Q404" s="1"/>
       <c r="R404" s="1"/>
       <c r="S404" s="1"/>
-      <c r="T404" s="1"/>
+      <c r="T404" s="24"/>
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
       <c r="W404" s="1"/>
@@ -27649,7 +27846,7 @@
       <c r="Q405" s="1"/>
       <c r="R405" s="1"/>
       <c r="S405" s="1"/>
-      <c r="T405" s="1"/>
+      <c r="T405" s="24"/>
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
       <c r="W405" s="1"/>
@@ -27704,7 +27901,7 @@
       <c r="Q406" s="1"/>
       <c r="R406" s="1"/>
       <c r="S406" s="1"/>
-      <c r="T406" s="1"/>
+      <c r="T406" s="24"/>
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
       <c r="W406" s="1"/>
@@ -27759,7 +27956,7 @@
       <c r="Q407" s="1"/>
       <c r="R407" s="1"/>
       <c r="S407" s="1"/>
-      <c r="T407" s="1"/>
+      <c r="T407" s="24"/>
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
       <c r="W407" s="1"/>
@@ -27814,7 +28011,7 @@
       <c r="Q408" s="1"/>
       <c r="R408" s="1"/>
       <c r="S408" s="1"/>
-      <c r="T408" s="1"/>
+      <c r="T408" s="24"/>
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
       <c r="W408" s="1"/>
@@ -27869,7 +28066,7 @@
       <c r="Q409" s="1"/>
       <c r="R409" s="1"/>
       <c r="S409" s="1"/>
-      <c r="T409" s="1"/>
+      <c r="T409" s="24"/>
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
       <c r="W409" s="1"/>
@@ -27924,7 +28121,7 @@
       <c r="Q410" s="1"/>
       <c r="R410" s="1"/>
       <c r="S410" s="1"/>
-      <c r="T410" s="1"/>
+      <c r="T410" s="24"/>
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
       <c r="W410" s="1"/>
@@ -27979,7 +28176,7 @@
       <c r="Q411" s="1"/>
       <c r="R411" s="1"/>
       <c r="S411" s="1"/>
-      <c r="T411" s="1"/>
+      <c r="T411" s="24"/>
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
       <c r="W411" s="1"/>
@@ -28034,7 +28231,7 @@
       <c r="Q412" s="1"/>
       <c r="R412" s="1"/>
       <c r="S412" s="1"/>
-      <c r="T412" s="1"/>
+      <c r="T412" s="24"/>
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
       <c r="W412" s="1"/>
@@ -28089,7 +28286,7 @@
       <c r="Q413" s="1"/>
       <c r="R413" s="1"/>
       <c r="S413" s="1"/>
-      <c r="T413" s="1"/>
+      <c r="T413" s="24"/>
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
       <c r="W413" s="1"/>
@@ -28144,7 +28341,7 @@
       <c r="Q414" s="1"/>
       <c r="R414" s="1"/>
       <c r="S414" s="1"/>
-      <c r="T414" s="1"/>
+      <c r="T414" s="24"/>
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
       <c r="W414" s="1"/>
@@ -28199,7 +28396,7 @@
       <c r="Q415" s="1"/>
       <c r="R415" s="1"/>
       <c r="S415" s="1"/>
-      <c r="T415" s="1"/>
+      <c r="T415" s="24"/>
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
       <c r="W415" s="1"/>
@@ -28254,7 +28451,7 @@
       <c r="Q416" s="1"/>
       <c r="R416" s="1"/>
       <c r="S416" s="1"/>
-      <c r="T416" s="1"/>
+      <c r="T416" s="24"/>
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
       <c r="W416" s="1"/>
@@ -28309,7 +28506,7 @@
       <c r="Q417" s="1"/>
       <c r="R417" s="1"/>
       <c r="S417" s="1"/>
-      <c r="T417" s="1"/>
+      <c r="T417" s="24"/>
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
       <c r="W417" s="1"/>
@@ -28364,7 +28561,7 @@
       <c r="Q418" s="1"/>
       <c r="R418" s="1"/>
       <c r="S418" s="1"/>
-      <c r="T418" s="1"/>
+      <c r="T418" s="24"/>
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
       <c r="W418" s="1"/>
@@ -28419,7 +28616,7 @@
       <c r="Q419" s="1"/>
       <c r="R419" s="1"/>
       <c r="S419" s="1"/>
-      <c r="T419" s="1"/>
+      <c r="T419" s="24"/>
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
       <c r="W419" s="1"/>
@@ -28474,7 +28671,7 @@
       <c r="Q420" s="1"/>
       <c r="R420" s="1"/>
       <c r="S420" s="1"/>
-      <c r="T420" s="1"/>
+      <c r="T420" s="24"/>
       <c r="U420" s="1"/>
       <c r="V420" s="1"/>
       <c r="W420" s="1"/>
@@ -28529,7 +28726,7 @@
       <c r="Q421" s="1"/>
       <c r="R421" s="1"/>
       <c r="S421" s="1"/>
-      <c r="T421" s="1"/>
+      <c r="T421" s="24"/>
       <c r="U421" s="1"/>
       <c r="V421" s="1"/>
       <c r="W421" s="1"/>
@@ -28584,7 +28781,7 @@
       <c r="Q422" s="1"/>
       <c r="R422" s="1"/>
       <c r="S422" s="1"/>
-      <c r="T422" s="1"/>
+      <c r="T422" s="24"/>
       <c r="U422" s="1"/>
       <c r="V422" s="1"/>
       <c r="W422" s="1"/>
@@ -28639,7 +28836,7 @@
       <c r="Q423" s="1"/>
       <c r="R423" s="1"/>
       <c r="S423" s="1"/>
-      <c r="T423" s="1"/>
+      <c r="T423" s="24"/>
       <c r="U423" s="1"/>
       <c r="V423" s="1"/>
       <c r="W423" s="1"/>
@@ -28694,7 +28891,7 @@
       <c r="Q424" s="1"/>
       <c r="R424" s="1"/>
       <c r="S424" s="1"/>
-      <c r="T424" s="1"/>
+      <c r="T424" s="24"/>
       <c r="U424" s="1"/>
       <c r="V424" s="1"/>
       <c r="W424" s="1"/>
@@ -28749,7 +28946,7 @@
       <c r="Q425" s="1"/>
       <c r="R425" s="1"/>
       <c r="S425" s="1"/>
-      <c r="T425" s="1"/>
+      <c r="T425" s="24"/>
       <c r="U425" s="1"/>
       <c r="V425" s="1"/>
       <c r="W425" s="1"/>
@@ -28804,7 +29001,7 @@
       <c r="Q426" s="1"/>
       <c r="R426" s="1"/>
       <c r="S426" s="1"/>
-      <c r="T426" s="1"/>
+      <c r="T426" s="24"/>
       <c r="U426" s="1"/>
       <c r="V426" s="1"/>
       <c r="W426" s="1"/>
@@ -28859,7 +29056,7 @@
       <c r="Q427" s="1"/>
       <c r="R427" s="1"/>
       <c r="S427" s="1"/>
-      <c r="T427" s="1"/>
+      <c r="T427" s="24"/>
       <c r="U427" s="1"/>
       <c r="V427" s="1"/>
       <c r="W427" s="1"/>
@@ -28914,7 +29111,7 @@
       <c r="Q428" s="1"/>
       <c r="R428" s="1"/>
       <c r="S428" s="1"/>
-      <c r="T428" s="1"/>
+      <c r="T428" s="24"/>
       <c r="U428" s="1"/>
       <c r="V428" s="1"/>
       <c r="W428" s="1"/>
@@ -28969,7 +29166,7 @@
       <c r="Q429" s="1"/>
       <c r="R429" s="1"/>
       <c r="S429" s="1"/>
-      <c r="T429" s="1"/>
+      <c r="T429" s="24"/>
       <c r="U429" s="1"/>
       <c r="V429" s="1"/>
       <c r="W429" s="1"/>
@@ -29024,7 +29221,7 @@
       <c r="Q430" s="1"/>
       <c r="R430" s="1"/>
       <c r="S430" s="1"/>
-      <c r="T430" s="1"/>
+      <c r="T430" s="24"/>
       <c r="U430" s="1"/>
       <c r="V430" s="1"/>
       <c r="W430" s="1"/>
@@ -29079,7 +29276,7 @@
       <c r="Q431" s="1"/>
       <c r="R431" s="1"/>
       <c r="S431" s="1"/>
-      <c r="T431" s="1"/>
+      <c r="T431" s="24"/>
       <c r="U431" s="1"/>
       <c r="V431" s="1"/>
       <c r="W431" s="1"/>
@@ -29134,7 +29331,7 @@
       <c r="Q432" s="1"/>
       <c r="R432" s="1"/>
       <c r="S432" s="1"/>
-      <c r="T432" s="1"/>
+      <c r="T432" s="24"/>
       <c r="U432" s="1"/>
       <c r="V432" s="1"/>
       <c r="W432" s="1"/>
@@ -29189,7 +29386,7 @@
       <c r="Q433" s="1"/>
       <c r="R433" s="1"/>
       <c r="S433" s="1"/>
-      <c r="T433" s="1"/>
+      <c r="T433" s="24"/>
       <c r="U433" s="1"/>
       <c r="V433" s="1"/>
       <c r="W433" s="1"/>
@@ -29244,7 +29441,7 @@
       <c r="Q434" s="1"/>
       <c r="R434" s="1"/>
       <c r="S434" s="1"/>
-      <c r="T434" s="1"/>
+      <c r="T434" s="24"/>
       <c r="U434" s="1"/>
       <c r="V434" s="1"/>
       <c r="W434" s="1"/>
@@ -29299,7 +29496,7 @@
       <c r="Q435" s="1"/>
       <c r="R435" s="1"/>
       <c r="S435" s="1"/>
-      <c r="T435" s="1"/>
+      <c r="T435" s="24"/>
       <c r="U435" s="1"/>
       <c r="V435" s="1"/>
       <c r="W435" s="1"/>
@@ -29354,7 +29551,7 @@
       <c r="Q436" s="1"/>
       <c r="R436" s="1"/>
       <c r="S436" s="1"/>
-      <c r="T436" s="1"/>
+      <c r="T436" s="24"/>
       <c r="U436" s="1"/>
       <c r="V436" s="1"/>
       <c r="W436" s="1"/>
@@ -29409,7 +29606,7 @@
       <c r="Q437" s="1"/>
       <c r="R437" s="1"/>
       <c r="S437" s="1"/>
-      <c r="T437" s="1"/>
+      <c r="T437" s="24"/>
       <c r="U437" s="1"/>
       <c r="V437" s="1"/>
       <c r="W437" s="1"/>
@@ -29464,7 +29661,7 @@
       <c r="Q438" s="1"/>
       <c r="R438" s="1"/>
       <c r="S438" s="1"/>
-      <c r="T438" s="1"/>
+      <c r="T438" s="24"/>
       <c r="U438" s="1"/>
       <c r="V438" s="1"/>
       <c r="W438" s="1"/>
@@ -29519,7 +29716,7 @@
       <c r="Q439" s="1"/>
       <c r="R439" s="1"/>
       <c r="S439" s="1"/>
-      <c r="T439" s="1"/>
+      <c r="T439" s="24"/>
       <c r="U439" s="1"/>
       <c r="V439" s="1"/>
       <c r="W439" s="1"/>
@@ -29574,7 +29771,7 @@
       <c r="Q440" s="1"/>
       <c r="R440" s="1"/>
       <c r="S440" s="1"/>
-      <c r="T440" s="1"/>
+      <c r="T440" s="24"/>
       <c r="U440" s="1"/>
       <c r="V440" s="1"/>
       <c r="W440" s="1"/>
@@ -29629,7 +29826,7 @@
       <c r="Q441" s="1"/>
       <c r="R441" s="1"/>
       <c r="S441" s="1"/>
-      <c r="T441" s="1"/>
+      <c r="T441" s="24"/>
       <c r="U441" s="1"/>
       <c r="V441" s="1"/>
       <c r="W441" s="1"/>
@@ -29684,7 +29881,7 @@
       <c r="Q442" s="1"/>
       <c r="R442" s="1"/>
       <c r="S442" s="1"/>
-      <c r="T442" s="1"/>
+      <c r="T442" s="24"/>
       <c r="U442" s="1"/>
       <c r="V442" s="1"/>
       <c r="W442" s="1"/>
@@ -29739,7 +29936,7 @@
       <c r="Q443" s="1"/>
       <c r="R443" s="1"/>
       <c r="S443" s="1"/>
-      <c r="T443" s="1"/>
+      <c r="T443" s="24"/>
       <c r="U443" s="1"/>
       <c r="V443" s="1"/>
       <c r="W443" s="1"/>
@@ -29794,7 +29991,7 @@
       <c r="Q444" s="1"/>
       <c r="R444" s="1"/>
       <c r="S444" s="1"/>
-      <c r="T444" s="1"/>
+      <c r="T444" s="24"/>
       <c r="U444" s="1"/>
       <c r="V444" s="1"/>
       <c r="W444" s="1"/>
@@ -29849,7 +30046,7 @@
       <c r="Q445" s="1"/>
       <c r="R445" s="1"/>
       <c r="S445" s="1"/>
-      <c r="T445" s="1"/>
+      <c r="T445" s="24"/>
       <c r="U445" s="1"/>
       <c r="V445" s="1"/>
       <c r="W445" s="1"/>
@@ -29904,7 +30101,7 @@
       <c r="Q446" s="1"/>
       <c r="R446" s="1"/>
       <c r="S446" s="1"/>
-      <c r="T446" s="1"/>
+      <c r="T446" s="24"/>
       <c r="U446" s="1"/>
       <c r="V446" s="1"/>
       <c r="W446" s="1"/>
@@ -29959,7 +30156,7 @@
       <c r="Q447" s="1"/>
       <c r="R447" s="1"/>
       <c r="S447" s="1"/>
-      <c r="T447" s="1"/>
+      <c r="T447" s="24"/>
       <c r="U447" s="1"/>
       <c r="V447" s="1"/>
       <c r="W447" s="1"/>
@@ -30014,7 +30211,7 @@
       <c r="Q448" s="1"/>
       <c r="R448" s="1"/>
       <c r="S448" s="1"/>
-      <c r="T448" s="1"/>
+      <c r="T448" s="24"/>
       <c r="U448" s="1"/>
       <c r="V448" s="1"/>
       <c r="W448" s="1"/>
@@ -30069,7 +30266,7 @@
       <c r="Q449" s="1"/>
       <c r="R449" s="1"/>
       <c r="S449" s="1"/>
-      <c r="T449" s="1"/>
+      <c r="T449" s="24"/>
       <c r="U449" s="1"/>
       <c r="V449" s="1"/>
       <c r="W449" s="1"/>
@@ -30124,7 +30321,7 @@
       <c r="Q450" s="1"/>
       <c r="R450" s="1"/>
       <c r="S450" s="1"/>
-      <c r="T450" s="1"/>
+      <c r="T450" s="24"/>
       <c r="U450" s="1"/>
       <c r="V450" s="1"/>
       <c r="W450" s="1"/>
@@ -30179,7 +30376,7 @@
       <c r="Q451" s="1"/>
       <c r="R451" s="1"/>
       <c r="S451" s="1"/>
-      <c r="T451" s="1"/>
+      <c r="T451" s="24"/>
       <c r="U451" s="1"/>
       <c r="V451" s="1"/>
       <c r="W451" s="1"/>
@@ -30234,7 +30431,7 @@
       <c r="Q452" s="1"/>
       <c r="R452" s="1"/>
       <c r="S452" s="1"/>
-      <c r="T452" s="1"/>
+      <c r="T452" s="24"/>
       <c r="U452" s="1"/>
       <c r="V452" s="1"/>
       <c r="W452" s="1"/>
@@ -30289,7 +30486,7 @@
       <c r="Q453" s="1"/>
       <c r="R453" s="1"/>
       <c r="S453" s="1"/>
-      <c r="T453" s="1"/>
+      <c r="T453" s="24"/>
       <c r="U453" s="1"/>
       <c r="V453" s="1"/>
       <c r="W453" s="1"/>
@@ -30344,7 +30541,7 @@
       <c r="Q454" s="1"/>
       <c r="R454" s="1"/>
       <c r="S454" s="1"/>
-      <c r="T454" s="1"/>
+      <c r="T454" s="24"/>
       <c r="U454" s="1"/>
       <c r="V454" s="1"/>
       <c r="W454" s="1"/>
@@ -30399,7 +30596,7 @@
       <c r="Q455" s="1"/>
       <c r="R455" s="1"/>
       <c r="S455" s="1"/>
-      <c r="T455" s="1"/>
+      <c r="T455" s="24"/>
       <c r="U455" s="1"/>
       <c r="V455" s="1"/>
       <c r="W455" s="1"/>
@@ -30454,7 +30651,7 @@
       <c r="Q456" s="1"/>
       <c r="R456" s="1"/>
       <c r="S456" s="1"/>
-      <c r="T456" s="1"/>
+      <c r="T456" s="24"/>
       <c r="U456" s="1"/>
       <c r="V456" s="1"/>
       <c r="W456" s="1"/>
@@ -30509,7 +30706,7 @@
       <c r="Q457" s="1"/>
       <c r="R457" s="1"/>
       <c r="S457" s="1"/>
-      <c r="T457" s="1"/>
+      <c r="T457" s="24"/>
       <c r="U457" s="1"/>
       <c r="V457" s="1"/>
       <c r="W457" s="1"/>
@@ -30564,7 +30761,7 @@
       <c r="Q458" s="1"/>
       <c r="R458" s="1"/>
       <c r="S458" s="1"/>
-      <c r="T458" s="1"/>
+      <c r="T458" s="24"/>
       <c r="U458" s="1"/>
       <c r="V458" s="1"/>
       <c r="W458" s="1"/>
@@ -30619,7 +30816,7 @@
       <c r="Q459" s="1"/>
       <c r="R459" s="1"/>
       <c r="S459" s="1"/>
-      <c r="T459" s="1"/>
+      <c r="T459" s="24"/>
       <c r="U459" s="1"/>
       <c r="V459" s="1"/>
       <c r="W459" s="1"/>
@@ -30674,7 +30871,7 @@
       <c r="Q460" s="1"/>
       <c r="R460" s="1"/>
       <c r="S460" s="1"/>
-      <c r="T460" s="1"/>
+      <c r="T460" s="24"/>
       <c r="U460" s="1"/>
       <c r="V460" s="1"/>
       <c r="W460" s="1"/>
@@ -30729,7 +30926,7 @@
       <c r="Q461" s="1"/>
       <c r="R461" s="1"/>
       <c r="S461" s="1"/>
-      <c r="T461" s="1"/>
+      <c r="T461" s="24"/>
       <c r="U461" s="1"/>
       <c r="V461" s="1"/>
       <c r="W461" s="1"/>
@@ -30784,7 +30981,7 @@
       <c r="Q462" s="1"/>
       <c r="R462" s="1"/>
       <c r="S462" s="1"/>
-      <c r="T462" s="1"/>
+      <c r="T462" s="24"/>
       <c r="U462" s="1"/>
       <c r="V462" s="1"/>
       <c r="W462" s="1"/>
@@ -30839,7 +31036,7 @@
       <c r="Q463" s="1"/>
       <c r="R463" s="1"/>
       <c r="S463" s="1"/>
-      <c r="T463" s="1"/>
+      <c r="T463" s="24"/>
       <c r="U463" s="1"/>
       <c r="V463" s="1"/>
       <c r="W463" s="1"/>
@@ -30894,7 +31091,7 @@
       <c r="Q464" s="1"/>
       <c r="R464" s="1"/>
       <c r="S464" s="1"/>
-      <c r="T464" s="1"/>
+      <c r="T464" s="24"/>
       <c r="U464" s="1"/>
       <c r="V464" s="1"/>
       <c r="W464" s="1"/>
@@ -30949,7 +31146,7 @@
       <c r="Q465" s="1"/>
       <c r="R465" s="1"/>
       <c r="S465" s="1"/>
-      <c r="T465" s="1"/>
+      <c r="T465" s="24"/>
       <c r="U465" s="1"/>
       <c r="V465" s="1"/>
       <c r="W465" s="1"/>
@@ -31004,7 +31201,7 @@
       <c r="Q466" s="1"/>
       <c r="R466" s="1"/>
       <c r="S466" s="1"/>
-      <c r="T466" s="1"/>
+      <c r="T466" s="24"/>
       <c r="U466" s="1"/>
       <c r="V466" s="1"/>
       <c r="W466" s="1"/>
@@ -31059,7 +31256,7 @@
       <c r="Q467" s="1"/>
       <c r="R467" s="1"/>
       <c r="S467" s="1"/>
-      <c r="T467" s="1"/>
+      <c r="T467" s="24"/>
       <c r="U467" s="1"/>
       <c r="V467" s="1"/>
       <c r="W467" s="1"/>
@@ -31114,7 +31311,7 @@
       <c r="Q468" s="1"/>
       <c r="R468" s="1"/>
       <c r="S468" s="1"/>
-      <c r="T468" s="1"/>
+      <c r="T468" s="24"/>
       <c r="U468" s="1"/>
       <c r="V468" s="1"/>
       <c r="W468" s="1"/>
@@ -31169,7 +31366,7 @@
       <c r="Q469" s="1"/>
       <c r="R469" s="1"/>
       <c r="S469" s="1"/>
-      <c r="T469" s="1"/>
+      <c r="T469" s="24"/>
       <c r="U469" s="1"/>
       <c r="V469" s="1"/>
       <c r="W469" s="1"/>
@@ -31224,7 +31421,7 @@
       <c r="Q470" s="1"/>
       <c r="R470" s="1"/>
       <c r="S470" s="1"/>
-      <c r="T470" s="1"/>
+      <c r="T470" s="24"/>
       <c r="U470" s="1"/>
       <c r="V470" s="1"/>
       <c r="W470" s="1"/>
@@ -31279,7 +31476,7 @@
       <c r="Q471" s="1"/>
       <c r="R471" s="1"/>
       <c r="S471" s="1"/>
-      <c r="T471" s="1"/>
+      <c r="T471" s="24"/>
       <c r="U471" s="1"/>
       <c r="V471" s="1"/>
       <c r="W471" s="1"/>
@@ -31334,7 +31531,7 @@
       <c r="Q472" s="1"/>
       <c r="R472" s="1"/>
       <c r="S472" s="1"/>
-      <c r="T472" s="1"/>
+      <c r="T472" s="24"/>
       <c r="U472" s="1"/>
       <c r="V472" s="1"/>
       <c r="W472" s="1"/>
@@ -31389,7 +31586,7 @@
       <c r="Q473" s="1"/>
       <c r="R473" s="1"/>
       <c r="S473" s="1"/>
-      <c r="T473" s="1"/>
+      <c r="T473" s="24"/>
       <c r="U473" s="1"/>
       <c r="V473" s="1"/>
       <c r="W473" s="1"/>
@@ -31444,7 +31641,7 @@
       <c r="Q474" s="1"/>
       <c r="R474" s="1"/>
       <c r="S474" s="1"/>
-      <c r="T474" s="1"/>
+      <c r="T474" s="24"/>
       <c r="U474" s="1"/>
       <c r="V474" s="1"/>
       <c r="W474" s="1"/>
@@ -31499,7 +31696,7 @@
       <c r="Q475" s="1"/>
       <c r="R475" s="1"/>
       <c r="S475" s="1"/>
-      <c r="T475" s="1"/>
+      <c r="T475" s="24"/>
       <c r="U475" s="1"/>
       <c r="V475" s="1"/>
       <c r="W475" s="1"/>
@@ -31554,7 +31751,7 @@
       <c r="Q476" s="1"/>
       <c r="R476" s="1"/>
       <c r="S476" s="1"/>
-      <c r="T476" s="1"/>
+      <c r="T476" s="24"/>
       <c r="U476" s="1"/>
       <c r="V476" s="1"/>
       <c r="W476" s="1"/>
@@ -31609,7 +31806,7 @@
       <c r="Q477" s="1"/>
       <c r="R477" s="1"/>
       <c r="S477" s="1"/>
-      <c r="T477" s="1"/>
+      <c r="T477" s="24"/>
       <c r="U477" s="1"/>
       <c r="V477" s="1"/>
       <c r="W477" s="1"/>
@@ -31664,7 +31861,7 @@
       <c r="Q478" s="1"/>
       <c r="R478" s="1"/>
       <c r="S478" s="1"/>
-      <c r="T478" s="1"/>
+      <c r="T478" s="24"/>
       <c r="U478" s="1"/>
       <c r="V478" s="1"/>
       <c r="W478" s="1"/>
@@ -31719,7 +31916,7 @@
       <c r="Q479" s="1"/>
       <c r="R479" s="1"/>
       <c r="S479" s="1"/>
-      <c r="T479" s="1"/>
+      <c r="T479" s="24"/>
       <c r="U479" s="1"/>
       <c r="V479" s="1"/>
       <c r="W479" s="1"/>
@@ -31774,7 +31971,7 @@
       <c r="Q480" s="1"/>
       <c r="R480" s="1"/>
       <c r="S480" s="1"/>
-      <c r="T480" s="1"/>
+      <c r="T480" s="24"/>
       <c r="U480" s="1"/>
       <c r="V480" s="1"/>
       <c r="W480" s="1"/>
@@ -31829,7 +32026,7 @@
       <c r="Q481" s="1"/>
       <c r="R481" s="1"/>
       <c r="S481" s="1"/>
-      <c r="T481" s="1"/>
+      <c r="T481" s="24"/>
       <c r="U481" s="1"/>
       <c r="V481" s="1"/>
       <c r="W481" s="1"/>
@@ -31884,7 +32081,7 @@
       <c r="Q482" s="1"/>
       <c r="R482" s="1"/>
       <c r="S482" s="1"/>
-      <c r="T482" s="1"/>
+      <c r="T482" s="24"/>
       <c r="U482" s="1"/>
       <c r="V482" s="1"/>
       <c r="W482" s="1"/>
@@ -31939,7 +32136,7 @@
       <c r="Q483" s="1"/>
       <c r="R483" s="1"/>
       <c r="S483" s="1"/>
-      <c r="T483" s="1"/>
+      <c r="T483" s="24"/>
       <c r="U483" s="1"/>
       <c r="V483" s="1"/>
       <c r="W483" s="1"/>
@@ -31994,7 +32191,7 @@
       <c r="Q484" s="1"/>
       <c r="R484" s="1"/>
       <c r="S484" s="1"/>
-      <c r="T484" s="1"/>
+      <c r="T484" s="24"/>
       <c r="U484" s="1"/>
       <c r="V484" s="1"/>
       <c r="W484" s="1"/>
@@ -32049,7 +32246,7 @@
       <c r="Q485" s="1"/>
       <c r="R485" s="1"/>
       <c r="S485" s="1"/>
-      <c r="T485" s="1"/>
+      <c r="T485" s="24"/>
       <c r="U485" s="1"/>
       <c r="V485" s="1"/>
       <c r="W485" s="1"/>
@@ -32104,7 +32301,7 @@
       <c r="Q486" s="1"/>
       <c r="R486" s="1"/>
       <c r="S486" s="1"/>
-      <c r="T486" s="1"/>
+      <c r="T486" s="24"/>
       <c r="U486" s="1"/>
       <c r="V486" s="1"/>
       <c r="W486" s="1"/>
@@ -32159,7 +32356,7 @@
       <c r="Q487" s="1"/>
       <c r="R487" s="1"/>
       <c r="S487" s="1"/>
-      <c r="T487" s="1"/>
+      <c r="T487" s="24"/>
       <c r="U487" s="1"/>
       <c r="V487" s="1"/>
       <c r="W487" s="1"/>
@@ -32214,7 +32411,7 @@
       <c r="Q488" s="1"/>
       <c r="R488" s="1"/>
       <c r="S488" s="1"/>
-      <c r="T488" s="1"/>
+      <c r="T488" s="24"/>
       <c r="U488" s="1"/>
       <c r="V488" s="1"/>
       <c r="W488" s="1"/>
@@ -32269,7 +32466,7 @@
       <c r="Q489" s="1"/>
       <c r="R489" s="1"/>
       <c r="S489" s="1"/>
-      <c r="T489" s="1"/>
+      <c r="T489" s="24"/>
       <c r="U489" s="1"/>
       <c r="V489" s="1"/>
       <c r="W489" s="1"/>
@@ -32324,7 +32521,7 @@
       <c r="Q490" s="1"/>
       <c r="R490" s="1"/>
       <c r="S490" s="1"/>
-      <c r="T490" s="1"/>
+      <c r="T490" s="24"/>
       <c r="U490" s="1"/>
       <c r="V490" s="1"/>
       <c r="W490" s="1"/>
@@ -32379,7 +32576,7 @@
       <c r="Q491" s="1"/>
       <c r="R491" s="1"/>
       <c r="S491" s="1"/>
-      <c r="T491" s="1"/>
+      <c r="T491" s="24"/>
       <c r="U491" s="1"/>
       <c r="V491" s="1"/>
       <c r="W491" s="1"/>
@@ -32434,7 +32631,7 @@
       <c r="Q492" s="1"/>
       <c r="R492" s="1"/>
       <c r="S492" s="1"/>
-      <c r="T492" s="1"/>
+      <c r="T492" s="24"/>
       <c r="U492" s="1"/>
       <c r="V492" s="1"/>
       <c r="W492" s="1"/>
@@ -32489,7 +32686,7 @@
       <c r="Q493" s="1"/>
       <c r="R493" s="1"/>
       <c r="S493" s="1"/>
-      <c r="T493" s="1"/>
+      <c r="T493" s="24"/>
       <c r="U493" s="1"/>
       <c r="V493" s="1"/>
       <c r="W493" s="1"/>
@@ -32544,7 +32741,7 @@
       <c r="Q494" s="1"/>
       <c r="R494" s="1"/>
       <c r="S494" s="1"/>
-      <c r="T494" s="1"/>
+      <c r="T494" s="24"/>
       <c r="U494" s="1"/>
       <c r="V494" s="1"/>
       <c r="W494" s="1"/>
@@ -32599,7 +32796,7 @@
       <c r="Q495" s="1"/>
       <c r="R495" s="1"/>
       <c r="S495" s="1"/>
-      <c r="T495" s="1"/>
+      <c r="T495" s="24"/>
       <c r="U495" s="1"/>
       <c r="V495" s="1"/>
       <c r="W495" s="1"/>
@@ -32654,7 +32851,7 @@
       <c r="Q496" s="1"/>
       <c r="R496" s="1"/>
       <c r="S496" s="1"/>
-      <c r="T496" s="1"/>
+      <c r="T496" s="24"/>
       <c r="U496" s="1"/>
       <c r="V496" s="1"/>
       <c r="W496" s="1"/>
@@ -32709,7 +32906,7 @@
       <c r="Q497" s="1"/>
       <c r="R497" s="1"/>
       <c r="S497" s="1"/>
-      <c r="T497" s="1"/>
+      <c r="T497" s="24"/>
       <c r="U497" s="1"/>
       <c r="V497" s="1"/>
       <c r="W497" s="1"/>
@@ -32764,7 +32961,7 @@
       <c r="Q498" s="1"/>
       <c r="R498" s="1"/>
       <c r="S498" s="1"/>
-      <c r="T498" s="1"/>
+      <c r="T498" s="24"/>
       <c r="U498" s="1"/>
       <c r="V498" s="1"/>
       <c r="W498" s="1"/>
@@ -32819,7 +33016,7 @@
       <c r="Q499" s="1"/>
       <c r="R499" s="1"/>
       <c r="S499" s="1"/>
-      <c r="T499" s="1"/>
+      <c r="T499" s="24"/>
       <c r="U499" s="1"/>
       <c r="V499" s="1"/>
       <c r="W499" s="1"/>
@@ -32874,7 +33071,7 @@
       <c r="Q500" s="1"/>
       <c r="R500" s="1"/>
       <c r="S500" s="1"/>
-      <c r="T500" s="1"/>
+      <c r="T500" s="24"/>
       <c r="U500" s="1"/>
       <c r="V500" s="1"/>
       <c r="W500" s="1"/>
